--- a/docs/assets/assets/afl_players_2025.xlsx
+++ b/docs/assets/assets/afl_players_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FlutterProjects\my_app\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D125C9-AEE8-47D3-A488-35FA2E37AAD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C0CD5A-3B60-465F-9605-E89644BED28B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28215" yWindow="1905" windowWidth="21675" windowHeight="12120" xr2:uid="{665E5CEE-4E8C-4944-8463-360E9D61C4FF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{665E5CEE-4E8C-4944-8463-360E9D61C4FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -2210,9 +2210,6 @@
     <t>Geelong Cats</t>
   </si>
   <si>
-    <t>GWS GIants</t>
-  </si>
-  <si>
     <t>Lachlan Murphy</t>
   </si>
   <si>
@@ -4947,6 +4944,9 @@
   </si>
   <si>
     <t>CD_I1041619</t>
+  </si>
+  <si>
+    <t>GWS Giants</t>
   </si>
 </sst>
 </file>
@@ -5386,7 +5386,7 @@
         <v>719</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -5394,7 +5394,7 @@
         <v>319</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -5403,12 +5403,12 @@
         <v>2025</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>715</v>
@@ -5420,7 +5420,7 @@
         <v>2025</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -5437,7 +5437,7 @@
         <v>2025</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -5454,7 +5454,7 @@
         <v>2025</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -5471,7 +5471,7 @@
         <v>2025</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5488,7 +5488,7 @@
         <v>2025</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -5505,7 +5505,7 @@
         <v>2025</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -5522,7 +5522,7 @@
         <v>2025</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -5539,12 +5539,12 @@
         <v>2025</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>120</v>
@@ -5556,7 +5556,7 @@
         <v>2025</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5573,7 +5573,7 @@
         <v>2025</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -5590,7 +5590,7 @@
         <v>2025</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -5607,7 +5607,7 @@
         <v>2025</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -5624,12 +5624,12 @@
         <v>2025</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>708</v>
@@ -5641,7 +5641,7 @@
         <v>2025</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -5658,7 +5658,7 @@
         <v>2025</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -5675,12 +5675,12 @@
         <v>2025</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>706</v>
@@ -5692,7 +5692,7 @@
         <v>2025</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -5709,7 +5709,7 @@
         <v>2025</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -5726,7 +5726,7 @@
         <v>2025</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -5743,7 +5743,7 @@
         <v>2025</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -5760,7 +5760,7 @@
         <v>2025</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -5777,12 +5777,12 @@
         <v>2025</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>714</v>
@@ -5794,7 +5794,7 @@
         <v>2025</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -5811,7 +5811,7 @@
         <v>2025</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -5828,12 +5828,12 @@
         <v>2025</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>717</v>
@@ -5845,7 +5845,7 @@
         <v>2025</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -5862,7 +5862,7 @@
         <v>2025</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -5879,7 +5879,7 @@
         <v>2025</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -5896,7 +5896,7 @@
         <v>2025</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -5913,7 +5913,7 @@
         <v>2025</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -5930,12 +5930,12 @@
         <v>2025</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>714</v>
@@ -5947,7 +5947,7 @@
         <v>2025</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -5964,12 +5964,12 @@
         <v>2025</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>159</v>
@@ -5981,7 +5981,7 @@
         <v>2025</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -5998,7 +5998,7 @@
         <v>2025</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -6015,7 +6015,7 @@
         <v>2025</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -6032,7 +6032,7 @@
         <v>2025</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -6049,7 +6049,7 @@
         <v>2025</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -6066,7 +6066,7 @@
         <v>2025</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -6083,7 +6083,7 @@
         <v>2025</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -6100,7 +6100,7 @@
         <v>2025</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -6117,7 +6117,7 @@
         <v>2025</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -6134,7 +6134,7 @@
         <v>2025</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -6151,7 +6151,7 @@
         <v>2025</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -6168,7 +6168,7 @@
         <v>2025</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -6185,7 +6185,7 @@
         <v>2025</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -6202,7 +6202,7 @@
         <v>2025</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -6219,7 +6219,7 @@
         <v>2025</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -6236,12 +6236,12 @@
         <v>2025</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>706</v>
@@ -6253,7 +6253,7 @@
         <v>2025</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -6270,7 +6270,7 @@
         <v>2025</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -6287,7 +6287,7 @@
         <v>2025</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -6304,7 +6304,7 @@
         <v>2025</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -6321,7 +6321,7 @@
         <v>2025</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -6338,7 +6338,7 @@
         <v>2025</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -6355,12 +6355,12 @@
         <v>2025</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>715</v>
@@ -6372,7 +6372,7 @@
         <v>2025</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -6389,7 +6389,7 @@
         <v>2025</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -6406,7 +6406,7 @@
         <v>2025</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -6423,7 +6423,7 @@
         <v>2025</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -6440,7 +6440,7 @@
         <v>2025</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -6457,7 +6457,7 @@
         <v>2025</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -6474,7 +6474,7 @@
         <v>2025</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -6491,12 +6491,12 @@
         <v>2025</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>715</v>
@@ -6508,7 +6508,7 @@
         <v>2025</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -6525,7 +6525,7 @@
         <v>2025</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -6542,7 +6542,7 @@
         <v>2025</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -6559,7 +6559,7 @@
         <v>2025</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -6576,7 +6576,7 @@
         <v>2025</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -6593,12 +6593,12 @@
         <v>2025</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>714</v>
@@ -6607,7 +6607,7 @@
         <v>2025</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -6624,7 +6624,7 @@
         <v>2025</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -6641,7 +6641,7 @@
         <v>2025</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -6658,12 +6658,12 @@
         <v>2025</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>721</v>
@@ -6675,7 +6675,7 @@
         <v>2025</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -6692,7 +6692,7 @@
         <v>2025</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -6709,7 +6709,7 @@
         <v>2025</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -6726,7 +6726,7 @@
         <v>2025</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -6743,7 +6743,7 @@
         <v>2025</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -6760,7 +6760,7 @@
         <v>2025</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -6777,7 +6777,7 @@
         <v>2025</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -6794,7 +6794,7 @@
         <v>2025</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -6811,7 +6811,7 @@
         <v>2025</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -6819,7 +6819,7 @@
         <v>328</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C86">
         <v>16</v>
@@ -6828,7 +6828,7 @@
         <v>2025</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -6845,7 +6845,7 @@
         <v>2025</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -6862,12 +6862,12 @@
         <v>2025</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>40</v>
@@ -6879,7 +6879,7 @@
         <v>2025</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -6896,7 +6896,7 @@
         <v>2025</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -6913,12 +6913,12 @@
         <v>2025</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>711</v>
@@ -6930,7 +6930,7 @@
         <v>2025</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -6947,7 +6947,7 @@
         <v>2025</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -6964,7 +6964,7 @@
         <v>2025</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -6981,7 +6981,7 @@
         <v>2025</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -6998,7 +6998,7 @@
         <v>2025</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -7015,12 +7015,12 @@
         <v>2025</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>715</v>
@@ -7032,12 +7032,12 @@
         <v>2025</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>717</v>
@@ -7049,7 +7049,7 @@
         <v>2025</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -7066,7 +7066,7 @@
         <v>2025</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -7083,15 +7083,15 @@
         <v>2025</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C102">
         <v>8</v>
@@ -7100,7 +7100,7 @@
         <v>2025</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -7117,7 +7117,7 @@
         <v>2025</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -7125,7 +7125,7 @@
         <v>353</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C104">
         <v>46</v>
@@ -7134,7 +7134,7 @@
         <v>2025</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -7151,12 +7151,12 @@
         <v>2025</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>716</v>
@@ -7168,21 +7168,21 @@
         <v>2025</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>1635</v>
+      </c>
+      <c r="D107">
+        <v>2025</v>
+      </c>
+      <c r="E107" s="5" t="s">
         <v>1197</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>723</v>
-      </c>
-      <c r="D107">
-        <v>2025</v>
-      </c>
-      <c r="E107" s="5" t="s">
-        <v>1198</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -7199,7 +7199,7 @@
         <v>2025</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -7216,7 +7216,7 @@
         <v>2025</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
@@ -7233,7 +7233,7 @@
         <v>2025</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
@@ -7250,7 +7250,7 @@
         <v>2025</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
@@ -7267,12 +7267,12 @@
         <v>2025</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>722</v>
@@ -7284,7 +7284,7 @@
         <v>2025</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -7301,7 +7301,7 @@
         <v>2025</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -7318,7 +7318,7 @@
         <v>2025</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -7335,7 +7335,7 @@
         <v>2025</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
@@ -7352,7 +7352,7 @@
         <v>2025</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
@@ -7369,7 +7369,7 @@
         <v>2025</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -7386,7 +7386,7 @@
         <v>2025</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
@@ -7403,7 +7403,7 @@
         <v>2025</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
@@ -7420,7 +7420,7 @@
         <v>2025</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
@@ -7437,12 +7437,12 @@
         <v>2025</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>159</v>
@@ -7454,7 +7454,7 @@
         <v>2025</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
@@ -7471,7 +7471,7 @@
         <v>2025</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
@@ -7488,7 +7488,7 @@
         <v>2025</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
@@ -7505,7 +7505,7 @@
         <v>2025</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
@@ -7522,7 +7522,7 @@
         <v>2025</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
@@ -7539,12 +7539,12 @@
         <v>2025</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>40</v>
@@ -7556,7 +7556,7 @@
         <v>2025</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
@@ -7573,7 +7573,7 @@
         <v>2025</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
@@ -7590,7 +7590,7 @@
         <v>2025</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
@@ -7607,7 +7607,7 @@
         <v>2025</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -7624,7 +7624,7 @@
         <v>2025</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -7641,7 +7641,7 @@
         <v>2025</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
@@ -7658,7 +7658,7 @@
         <v>2025</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
@@ -7675,7 +7675,7 @@
         <v>2025</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -7683,7 +7683,7 @@
         <v>340</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C137">
         <v>29</v>
@@ -7692,7 +7692,7 @@
         <v>2025</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
@@ -7709,12 +7709,12 @@
         <v>2025</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>716</v>
@@ -7726,7 +7726,7 @@
         <v>2025</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
@@ -7743,7 +7743,7 @@
         <v>2025</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
@@ -7760,7 +7760,7 @@
         <v>2025</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
@@ -7768,7 +7768,7 @@
         <v>349</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C142">
         <v>39</v>
@@ -7777,7 +7777,7 @@
         <v>2025</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
@@ -7794,7 +7794,7 @@
         <v>2025</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
@@ -7811,7 +7811,7 @@
         <v>2025</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -7828,7 +7828,7 @@
         <v>2025</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
@@ -7845,7 +7845,7 @@
         <v>2025</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
@@ -7862,7 +7862,7 @@
         <v>2025</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
@@ -7870,7 +7870,7 @@
         <v>330</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C148">
         <v>18</v>
@@ -7879,7 +7879,7 @@
         <v>2025</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
@@ -7896,7 +7896,7 @@
         <v>2025</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
@@ -7913,7 +7913,7 @@
         <v>2025</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
@@ -7930,7 +7930,7 @@
         <v>2025</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
@@ -7947,7 +7947,7 @@
         <v>2025</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
@@ -7964,7 +7964,7 @@
         <v>2025</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
@@ -7981,7 +7981,7 @@
         <v>2025</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
@@ -7998,7 +7998,7 @@
         <v>2025</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
@@ -8015,7 +8015,7 @@
         <v>2025</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
@@ -8032,7 +8032,7 @@
         <v>2025</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
@@ -8049,7 +8049,7 @@
         <v>2025</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
@@ -8066,7 +8066,7 @@
         <v>2025</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
@@ -8083,7 +8083,7 @@
         <v>2025</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
@@ -8100,7 +8100,7 @@
         <v>2025</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
@@ -8117,7 +8117,7 @@
         <v>2025</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
@@ -8134,7 +8134,7 @@
         <v>2025</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
@@ -8151,7 +8151,7 @@
         <v>2025</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
@@ -8168,7 +8168,7 @@
         <v>2025</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
@@ -8185,7 +8185,7 @@
         <v>2025</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
@@ -8202,7 +8202,7 @@
         <v>2025</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
@@ -8219,12 +8219,12 @@
         <v>2025</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>721</v>
@@ -8236,7 +8236,7 @@
         <v>2025</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
@@ -8253,7 +8253,7 @@
         <v>2025</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
@@ -8270,7 +8270,7 @@
         <v>2025</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
@@ -8287,7 +8287,7 @@
         <v>2025</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
@@ -8295,7 +8295,7 @@
         <v>316</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C173">
         <v>2</v>
@@ -8304,7 +8304,7 @@
         <v>2025</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
@@ -8321,7 +8321,7 @@
         <v>2025</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
@@ -8338,12 +8338,12 @@
         <v>2025</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>711</v>
@@ -8355,7 +8355,7 @@
         <v>2025</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
@@ -8372,7 +8372,7 @@
         <v>2025</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
@@ -8389,7 +8389,7 @@
         <v>2025</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
@@ -8406,12 +8406,12 @@
         <v>2025</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>708</v>
@@ -8423,7 +8423,7 @@
         <v>2025</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
@@ -8440,7 +8440,7 @@
         <v>2025</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
@@ -8457,7 +8457,7 @@
         <v>2025</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
@@ -8474,12 +8474,12 @@
         <v>2025</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>716</v>
@@ -8491,7 +8491,7 @@
         <v>2025</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
@@ -8508,7 +8508,7 @@
         <v>2025</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
@@ -8525,12 +8525,12 @@
         <v>2025</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>706</v>
@@ -8542,7 +8542,7 @@
         <v>2025</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
@@ -8559,12 +8559,12 @@
         <v>2025</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>712</v>
@@ -8576,7 +8576,7 @@
         <v>2025</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
@@ -8593,7 +8593,7 @@
         <v>2025</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
@@ -8610,7 +8610,7 @@
         <v>2025</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
@@ -8627,7 +8627,7 @@
         <v>2025</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
@@ -8644,12 +8644,12 @@
         <v>2025</v>
       </c>
       <c r="E193" s="5" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>711</v>
@@ -8661,7 +8661,7 @@
         <v>2025</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
@@ -8678,12 +8678,12 @@
         <v>2025</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>120</v>
@@ -8695,7 +8695,7 @@
         <v>2025</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
@@ -8712,7 +8712,7 @@
         <v>2025</v>
       </c>
       <c r="E197" s="5" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
@@ -8729,7 +8729,7 @@
         <v>2025</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
@@ -8746,7 +8746,7 @@
         <v>2025</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
@@ -8763,7 +8763,7 @@
         <v>2025</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
@@ -8780,7 +8780,7 @@
         <v>2025</v>
       </c>
       <c r="E201" s="5" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
@@ -8797,7 +8797,7 @@
         <v>2025</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
@@ -8814,7 +8814,7 @@
         <v>2025</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
@@ -8831,7 +8831,7 @@
         <v>2025</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
@@ -8848,7 +8848,7 @@
         <v>2025</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
@@ -8856,7 +8856,7 @@
         <v>329</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C206">
         <v>17</v>
@@ -8865,7 +8865,7 @@
         <v>2025</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
@@ -8882,7 +8882,7 @@
         <v>2025</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
@@ -8899,7 +8899,7 @@
         <v>2025</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
@@ -8916,7 +8916,7 @@
         <v>2025</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
@@ -8933,7 +8933,7 @@
         <v>2025</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
@@ -8950,12 +8950,12 @@
         <v>2025</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>711</v>
@@ -8967,7 +8967,7 @@
         <v>2025</v>
       </c>
       <c r="E212" s="5" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
@@ -8984,7 +8984,7 @@
         <v>2025</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
@@ -9001,7 +9001,7 @@
         <v>2025</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
@@ -9018,7 +9018,7 @@
         <v>2025</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
@@ -9035,7 +9035,7 @@
         <v>2025</v>
       </c>
       <c r="E216" s="5" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
@@ -9052,7 +9052,7 @@
         <v>2025</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
@@ -9069,7 +9069,7 @@
         <v>2025</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
@@ -9086,7 +9086,7 @@
         <v>2025</v>
       </c>
       <c r="E219" s="5" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
@@ -9103,7 +9103,7 @@
         <v>2025</v>
       </c>
       <c r="E220" s="5" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
@@ -9120,21 +9120,21 @@
         <v>2025</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="5" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>1635</v>
+      </c>
+      <c r="D222">
+        <v>2025</v>
+      </c>
+      <c r="E222" s="5" t="s">
         <v>1202</v>
-      </c>
-      <c r="B222" s="1" t="s">
-        <v>723</v>
-      </c>
-      <c r="D222">
-        <v>2025</v>
-      </c>
-      <c r="E222" s="5" t="s">
-        <v>1203</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
@@ -9151,7 +9151,7 @@
         <v>2025</v>
       </c>
       <c r="E223" s="5" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
@@ -9168,7 +9168,7 @@
         <v>2025</v>
       </c>
       <c r="E224" s="5" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
@@ -9185,7 +9185,7 @@
         <v>2025</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
@@ -9202,7 +9202,7 @@
         <v>2025</v>
       </c>
       <c r="E226" s="5" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
@@ -9219,7 +9219,7 @@
         <v>2025</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
@@ -9236,7 +9236,7 @@
         <v>2025</v>
       </c>
       <c r="E228" s="5" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
@@ -9253,7 +9253,7 @@
         <v>2025</v>
       </c>
       <c r="E229" s="5" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
@@ -9270,7 +9270,7 @@
         <v>2025</v>
       </c>
       <c r="E230" s="5" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
@@ -9278,7 +9278,7 @@
         <v>338</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C231">
         <v>27</v>
@@ -9287,12 +9287,12 @@
         <v>2025</v>
       </c>
       <c r="E231" s="5" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B232" s="1" t="s">
         <v>120</v>
@@ -9304,7 +9304,7 @@
         <v>2025</v>
       </c>
       <c r="E232" s="5" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
@@ -9321,7 +9321,7 @@
         <v>2025</v>
       </c>
       <c r="E233" s="5" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
@@ -9338,7 +9338,7 @@
         <v>2025</v>
       </c>
       <c r="E234" s="5" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
@@ -9355,7 +9355,7 @@
         <v>2025</v>
       </c>
       <c r="E235" s="5" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
@@ -9363,7 +9363,7 @@
         <v>331</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C236">
         <v>19</v>
@@ -9372,7 +9372,7 @@
         <v>2025</v>
       </c>
       <c r="E236" s="5" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
@@ -9389,7 +9389,7 @@
         <v>2025</v>
       </c>
       <c r="E237" s="5" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
@@ -9397,7 +9397,7 @@
         <v>336</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C238">
         <v>24</v>
@@ -9406,7 +9406,7 @@
         <v>2025</v>
       </c>
       <c r="E238" s="5" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
@@ -9423,7 +9423,7 @@
         <v>2025</v>
       </c>
       <c r="E239" s="5" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
@@ -9440,7 +9440,7 @@
         <v>2025</v>
       </c>
       <c r="E240" s="5" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
@@ -9457,7 +9457,7 @@
         <v>2025</v>
       </c>
       <c r="E241" s="5" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
@@ -9474,7 +9474,7 @@
         <v>2025</v>
       </c>
       <c r="E242" s="5" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
@@ -9491,7 +9491,7 @@
         <v>2025</v>
       </c>
       <c r="E243" s="5" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
@@ -9508,7 +9508,7 @@
         <v>2025</v>
       </c>
       <c r="E244" s="5" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
@@ -9525,7 +9525,7 @@
         <v>2025</v>
       </c>
       <c r="E245" s="5" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
@@ -9533,7 +9533,7 @@
         <v>315</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -9542,7 +9542,7 @@
         <v>2025</v>
       </c>
       <c r="E246" s="5" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
@@ -9559,7 +9559,7 @@
         <v>2025</v>
       </c>
       <c r="E247" s="5" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
@@ -9576,7 +9576,7 @@
         <v>2025</v>
       </c>
       <c r="E248" s="5" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
@@ -9593,7 +9593,7 @@
         <v>2025</v>
       </c>
       <c r="E249" s="5" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
@@ -9610,7 +9610,7 @@
         <v>2025</v>
       </c>
       <c r="E250" s="5" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
@@ -9627,7 +9627,7 @@
         <v>2025</v>
       </c>
       <c r="E251" s="5" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
@@ -9644,7 +9644,7 @@
         <v>2025</v>
       </c>
       <c r="E252" s="5" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
@@ -9661,7 +9661,7 @@
         <v>2025</v>
       </c>
       <c r="E253" s="5" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
@@ -9678,7 +9678,7 @@
         <v>2025</v>
       </c>
       <c r="E254" s="5" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
@@ -9695,12 +9695,12 @@
         <v>2025</v>
       </c>
       <c r="E255" s="5" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B256" s="1" t="s">
         <v>712</v>
@@ -9712,7 +9712,7 @@
         <v>2025</v>
       </c>
       <c r="E256" s="5" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
@@ -9729,7 +9729,7 @@
         <v>2025</v>
       </c>
       <c r="E257" s="5" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
@@ -9746,7 +9746,7 @@
         <v>2025</v>
       </c>
       <c r="E258" s="5" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
@@ -9763,7 +9763,7 @@
         <v>2025</v>
       </c>
       <c r="E259" s="5" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
@@ -9780,7 +9780,7 @@
         <v>2025</v>
       </c>
       <c r="E260" s="5" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
@@ -9797,12 +9797,12 @@
         <v>2025</v>
       </c>
       <c r="E261" s="5" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B262" s="1" t="s">
         <v>715</v>
@@ -9814,7 +9814,7 @@
         <v>2025</v>
       </c>
       <c r="E262" s="5" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
@@ -9831,7 +9831,7 @@
         <v>2025</v>
       </c>
       <c r="E263" s="5" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
@@ -9848,7 +9848,7 @@
         <v>2025</v>
       </c>
       <c r="E264" s="5" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
@@ -9865,7 +9865,7 @@
         <v>2025</v>
       </c>
       <c r="E265" s="5" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
@@ -9882,7 +9882,7 @@
         <v>2025</v>
       </c>
       <c r="E266" s="5" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
@@ -9899,7 +9899,7 @@
         <v>2025</v>
       </c>
       <c r="E267" s="5" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
@@ -9916,7 +9916,7 @@
         <v>2025</v>
       </c>
       <c r="E268" s="5" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
@@ -9933,7 +9933,7 @@
         <v>2025</v>
       </c>
       <c r="E269" s="5" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
@@ -9950,12 +9950,12 @@
         <v>2025</v>
       </c>
       <c r="E270" s="5" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B271" s="1" t="s">
         <v>710</v>
@@ -9967,7 +9967,7 @@
         <v>2025</v>
       </c>
       <c r="E271" s="5" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
@@ -9984,7 +9984,7 @@
         <v>2025</v>
       </c>
       <c r="E272" s="5" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
@@ -9992,7 +9992,7 @@
         <v>352</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C273">
         <v>44</v>
@@ -10001,7 +10001,7 @@
         <v>2025</v>
       </c>
       <c r="E273" s="5" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
@@ -10018,7 +10018,7 @@
         <v>2025</v>
       </c>
       <c r="E274" s="5" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
@@ -10035,7 +10035,7 @@
         <v>2025</v>
       </c>
       <c r="E275" s="5" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
@@ -10052,7 +10052,7 @@
         <v>2025</v>
       </c>
       <c r="E276" s="5" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
@@ -10069,12 +10069,12 @@
         <v>2025</v>
       </c>
       <c r="E277" s="5" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B278" s="1" t="s">
         <v>707</v>
@@ -10086,7 +10086,7 @@
         <v>2025</v>
       </c>
       <c r="E278" s="5" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
@@ -10103,7 +10103,7 @@
         <v>2025</v>
       </c>
       <c r="E279" s="5" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.25">
@@ -10120,7 +10120,7 @@
         <v>2025</v>
       </c>
       <c r="E280" s="5" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.25">
@@ -10137,7 +10137,7 @@
         <v>2025</v>
       </c>
       <c r="E281" s="5" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
@@ -10154,7 +10154,7 @@
         <v>2025</v>
       </c>
       <c r="E282" s="5" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.25">
@@ -10171,7 +10171,7 @@
         <v>2025</v>
       </c>
       <c r="E283" s="5" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
@@ -10188,7 +10188,7 @@
         <v>2025</v>
       </c>
       <c r="E284" s="5" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.25">
@@ -10205,7 +10205,7 @@
         <v>2025</v>
       </c>
       <c r="E285" s="5" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.25">
@@ -10222,7 +10222,7 @@
         <v>2025</v>
       </c>
       <c r="E286" s="5" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
@@ -10239,7 +10239,7 @@
         <v>2025</v>
       </c>
       <c r="E287" s="5" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
@@ -10256,7 +10256,7 @@
         <v>2025</v>
       </c>
       <c r="E288" s="5" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
@@ -10264,7 +10264,7 @@
         <v>339</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C289">
         <v>28</v>
@@ -10273,7 +10273,7 @@
         <v>2025</v>
       </c>
       <c r="E289" s="5" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
@@ -10290,12 +10290,12 @@
         <v>2025</v>
       </c>
       <c r="E290" s="5" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B291" s="1" t="s">
         <v>716</v>
@@ -10307,7 +10307,7 @@
         <v>2025</v>
       </c>
       <c r="E291" s="5" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.25">
@@ -10324,7 +10324,7 @@
         <v>2025</v>
       </c>
       <c r="E292" s="5" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
@@ -10341,7 +10341,7 @@
         <v>2025</v>
       </c>
       <c r="E293" s="5" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
@@ -10358,7 +10358,7 @@
         <v>2025</v>
       </c>
       <c r="E294" s="5" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
@@ -10375,7 +10375,7 @@
         <v>2025</v>
       </c>
       <c r="E295" s="5" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
@@ -10392,7 +10392,7 @@
         <v>2025</v>
       </c>
       <c r="E296" s="5" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
@@ -10409,7 +10409,7 @@
         <v>2025</v>
       </c>
       <c r="E297" s="5" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
@@ -10426,7 +10426,7 @@
         <v>2025</v>
       </c>
       <c r="E298" s="5" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.25">
@@ -10443,7 +10443,7 @@
         <v>2025</v>
       </c>
       <c r="E299" s="5" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
@@ -10460,7 +10460,7 @@
         <v>2025</v>
       </c>
       <c r="E300" s="5" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.25">
@@ -10477,12 +10477,12 @@
         <v>2025</v>
       </c>
       <c r="E301" s="5" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B302" s="1" t="s">
         <v>713</v>
@@ -10494,12 +10494,12 @@
         <v>2025</v>
       </c>
       <c r="E302" s="5" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B303" s="1" t="s">
         <v>713</v>
@@ -10511,7 +10511,7 @@
         <v>2025</v>
       </c>
       <c r="E303" s="5" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
@@ -10528,7 +10528,7 @@
         <v>2025</v>
       </c>
       <c r="E304" s="5" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
@@ -10545,12 +10545,12 @@
         <v>2025</v>
       </c>
       <c r="E305" s="5" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B306" s="1" t="s">
         <v>713</v>
@@ -10562,7 +10562,7 @@
         <v>2025</v>
       </c>
       <c r="E306" s="5" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
@@ -10579,7 +10579,7 @@
         <v>2025</v>
       </c>
       <c r="E307" s="5" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.25">
@@ -10596,7 +10596,7 @@
         <v>2025</v>
       </c>
       <c r="E308" s="5" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
@@ -10613,7 +10613,7 @@
         <v>2025</v>
       </c>
       <c r="E309" s="5" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
@@ -10630,7 +10630,7 @@
         <v>2025</v>
       </c>
       <c r="E310" s="5" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
@@ -10638,7 +10638,7 @@
         <v>510</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C311">
         <v>10</v>
@@ -10647,7 +10647,7 @@
         <v>2025</v>
       </c>
       <c r="E311" s="5" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
@@ -10664,7 +10664,7 @@
         <v>2025</v>
       </c>
       <c r="E312" s="5" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
@@ -10681,7 +10681,7 @@
         <v>2025</v>
       </c>
       <c r="E313" s="5" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
@@ -10698,7 +10698,7 @@
         <v>2025</v>
       </c>
       <c r="E314" s="5" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
@@ -10715,7 +10715,7 @@
         <v>2025</v>
       </c>
       <c r="E315" s="5" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
@@ -10732,7 +10732,7 @@
         <v>2025</v>
       </c>
       <c r="E316" s="5" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.25">
@@ -10749,7 +10749,7 @@
         <v>2025</v>
       </c>
       <c r="E317" s="5" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
@@ -10766,7 +10766,7 @@
         <v>2025</v>
       </c>
       <c r="E318" s="5" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
@@ -10783,7 +10783,7 @@
         <v>2025</v>
       </c>
       <c r="E319" s="5" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
@@ -10800,7 +10800,7 @@
         <v>2025</v>
       </c>
       <c r="E320" s="5" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
@@ -10817,7 +10817,7 @@
         <v>2025</v>
       </c>
       <c r="E321" s="5" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
@@ -10834,7 +10834,7 @@
         <v>2025</v>
       </c>
       <c r="E322" s="5" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
@@ -10851,7 +10851,7 @@
         <v>2025</v>
       </c>
       <c r="E323" s="5" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
@@ -10868,7 +10868,7 @@
         <v>2025</v>
       </c>
       <c r="E324" s="5" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
@@ -10876,7 +10876,7 @@
         <v>337</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C325">
         <v>26</v>
@@ -10885,7 +10885,7 @@
         <v>2025</v>
       </c>
       <c r="E325" s="5" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.25">
@@ -10902,7 +10902,7 @@
         <v>2025</v>
       </c>
       <c r="E326" s="5" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
@@ -10919,7 +10919,7 @@
         <v>2025</v>
       </c>
       <c r="E327" s="5" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
@@ -10927,7 +10927,7 @@
         <v>332</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C328">
         <v>20</v>
@@ -10936,7 +10936,7 @@
         <v>2025</v>
       </c>
       <c r="E328" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
@@ -10953,7 +10953,7 @@
         <v>2025</v>
       </c>
       <c r="E329" s="5" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
@@ -10970,7 +10970,7 @@
         <v>2025</v>
       </c>
       <c r="E330" s="5" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
@@ -10987,12 +10987,12 @@
         <v>2025</v>
       </c>
       <c r="E331" s="5" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B332" s="1" t="s">
         <v>707</v>
@@ -11004,7 +11004,7 @@
         <v>2025</v>
       </c>
       <c r="E332" s="5" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
@@ -11021,7 +11021,7 @@
         <v>2025</v>
       </c>
       <c r="E333" s="5" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
@@ -11038,7 +11038,7 @@
         <v>2025</v>
       </c>
       <c r="E334" s="5" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.25">
@@ -11055,7 +11055,7 @@
         <v>2025</v>
       </c>
       <c r="E335" s="5" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.25">
@@ -11072,7 +11072,7 @@
         <v>2025</v>
       </c>
       <c r="E336" s="5" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
@@ -11089,7 +11089,7 @@
         <v>2025</v>
       </c>
       <c r="E337" s="5" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.25">
@@ -11097,7 +11097,7 @@
         <v>341</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C338">
         <v>30</v>
@@ -11106,7 +11106,7 @@
         <v>2025</v>
       </c>
       <c r="E338" s="5" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
@@ -11123,7 +11123,7 @@
         <v>2025</v>
       </c>
       <c r="E339" s="5" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.25">
@@ -11140,7 +11140,7 @@
         <v>2025</v>
       </c>
       <c r="E340" s="5" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.25">
@@ -11157,7 +11157,7 @@
         <v>2025</v>
       </c>
       <c r="E341" s="5" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
@@ -11174,7 +11174,7 @@
         <v>2025</v>
       </c>
       <c r="E342" s="5" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.25">
@@ -11191,7 +11191,7 @@
         <v>2025</v>
       </c>
       <c r="E343" s="5" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.25">
@@ -11208,7 +11208,7 @@
         <v>2025</v>
       </c>
       <c r="E344" s="5" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.25">
@@ -11225,7 +11225,7 @@
         <v>2025</v>
       </c>
       <c r="E345" s="5" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
@@ -11242,7 +11242,7 @@
         <v>2025</v>
       </c>
       <c r="E346" s="5" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.25">
@@ -11259,7 +11259,7 @@
         <v>2025</v>
       </c>
       <c r="E347" s="5" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.25">
@@ -11276,7 +11276,7 @@
         <v>2025</v>
       </c>
       <c r="E348" s="5" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.25">
@@ -11293,7 +11293,7 @@
         <v>2025</v>
       </c>
       <c r="E349" s="5" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.25">
@@ -11310,7 +11310,7 @@
         <v>2025</v>
       </c>
       <c r="E350" s="5" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
@@ -11327,7 +11327,7 @@
         <v>2025</v>
       </c>
       <c r="E351" s="5" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
@@ -11344,7 +11344,7 @@
         <v>2025</v>
       </c>
       <c r="E352" s="5" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.25">
@@ -11361,12 +11361,12 @@
         <v>2025</v>
       </c>
       <c r="E353" s="5" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B354" s="1" t="s">
         <v>717</v>
@@ -11378,7 +11378,7 @@
         <v>2025</v>
       </c>
       <c r="E354" s="5" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
@@ -11395,7 +11395,7 @@
         <v>2025</v>
       </c>
       <c r="E355" s="5" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.25">
@@ -11412,12 +11412,12 @@
         <v>2025</v>
       </c>
       <c r="E356" s="5" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B357" s="1" t="s">
         <v>709</v>
@@ -11429,12 +11429,12 @@
         <v>2025</v>
       </c>
       <c r="E357" s="5" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B358" s="1" t="s">
         <v>120</v>
@@ -11446,7 +11446,7 @@
         <v>2025</v>
       </c>
       <c r="E358" s="5" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
@@ -11463,7 +11463,7 @@
         <v>2025</v>
       </c>
       <c r="E359" s="5" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.25">
@@ -11480,12 +11480,12 @@
         <v>2025</v>
       </c>
       <c r="E360" s="5" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B361" s="1" t="s">
         <v>716</v>
@@ -11497,7 +11497,7 @@
         <v>2025</v>
       </c>
       <c r="E361" s="5" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.25">
@@ -11514,7 +11514,7 @@
         <v>2025</v>
       </c>
       <c r="E362" s="5" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
@@ -11531,7 +11531,7 @@
         <v>2025</v>
       </c>
       <c r="E363" s="5" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.25">
@@ -11548,7 +11548,7 @@
         <v>2025</v>
       </c>
       <c r="E364" s="5" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.25">
@@ -11565,7 +11565,7 @@
         <v>2025</v>
       </c>
       <c r="E365" s="5" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
@@ -11582,12 +11582,12 @@
         <v>2025</v>
       </c>
       <c r="E366" s="5" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B367" s="1" t="s">
         <v>712</v>
@@ -11599,7 +11599,7 @@
         <v>2025</v>
       </c>
       <c r="E367" s="5" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
@@ -11616,7 +11616,7 @@
         <v>2025</v>
       </c>
       <c r="E368" s="5" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
@@ -11633,7 +11633,7 @@
         <v>2025</v>
       </c>
       <c r="E369" s="5" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
@@ -11650,12 +11650,12 @@
         <v>2025</v>
       </c>
       <c r="E370" s="5" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B371" s="1" t="s">
         <v>712</v>
@@ -11667,7 +11667,7 @@
         <v>2025</v>
       </c>
       <c r="E371" s="5" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
@@ -11684,12 +11684,12 @@
         <v>2025</v>
       </c>
       <c r="E372" s="5" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B373" s="1" t="s">
         <v>716</v>
@@ -11701,7 +11701,7 @@
         <v>2025</v>
       </c>
       <c r="E373" s="5" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
@@ -11718,7 +11718,7 @@
         <v>2025</v>
       </c>
       <c r="E374" s="5" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
@@ -11735,7 +11735,7 @@
         <v>2025</v>
       </c>
       <c r="E375" s="5" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
@@ -11743,7 +11743,7 @@
         <v>335</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C376">
         <v>23</v>
@@ -11752,7 +11752,7 @@
         <v>2025</v>
       </c>
       <c r="E376" s="5" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
@@ -11769,7 +11769,7 @@
         <v>2025</v>
       </c>
       <c r="E377" s="5" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
@@ -11786,12 +11786,12 @@
         <v>2025</v>
       </c>
       <c r="E378" s="5" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B379" s="1" t="s">
         <v>714</v>
@@ -11803,7 +11803,7 @@
         <v>2025</v>
       </c>
       <c r="E379" s="5" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
@@ -11820,7 +11820,7 @@
         <v>2025</v>
       </c>
       <c r="E380" s="5" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
@@ -11837,7 +11837,7 @@
         <v>2025</v>
       </c>
       <c r="E381" s="5" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
@@ -11845,7 +11845,7 @@
         <v>347</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C382">
         <v>37</v>
@@ -11854,7 +11854,7 @@
         <v>2025</v>
       </c>
       <c r="E382" s="5" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
@@ -11871,7 +11871,7 @@
         <v>2025</v>
       </c>
       <c r="E383" s="5" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
@@ -11888,7 +11888,7 @@
         <v>2025</v>
       </c>
       <c r="E384" s="5" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
@@ -11905,7 +11905,7 @@
         <v>2025</v>
       </c>
       <c r="E385" s="5" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
@@ -11922,7 +11922,7 @@
         <v>2025</v>
       </c>
       <c r="E386" s="5" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
@@ -11939,7 +11939,7 @@
         <v>2025</v>
       </c>
       <c r="E387" s="5" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
@@ -11956,7 +11956,7 @@
         <v>2025</v>
       </c>
       <c r="E388" s="5" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
@@ -11973,7 +11973,7 @@
         <v>2025</v>
       </c>
       <c r="E389" s="5" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
@@ -11990,7 +11990,7 @@
         <v>2025</v>
       </c>
       <c r="E390" s="5" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
@@ -12007,7 +12007,7 @@
         <v>2025</v>
       </c>
       <c r="E391" s="5" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
@@ -12024,7 +12024,7 @@
         <v>2025</v>
       </c>
       <c r="E392" s="5" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
@@ -12041,7 +12041,7 @@
         <v>2025</v>
       </c>
       <c r="E393" s="5" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
@@ -12058,7 +12058,7 @@
         <v>2025</v>
       </c>
       <c r="E394" s="5" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
@@ -12075,7 +12075,7 @@
         <v>2025</v>
       </c>
       <c r="E395" s="5" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
@@ -12092,7 +12092,7 @@
         <v>2025</v>
       </c>
       <c r="E396" s="5" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
@@ -12109,7 +12109,7 @@
         <v>2025</v>
       </c>
       <c r="E397" s="5" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
@@ -12126,7 +12126,7 @@
         <v>2025</v>
       </c>
       <c r="E398" s="5" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
@@ -12143,7 +12143,7 @@
         <v>2025</v>
       </c>
       <c r="E399" s="5" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
@@ -12151,7 +12151,7 @@
         <v>348</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C400">
         <v>38</v>
@@ -12160,7 +12160,7 @@
         <v>2025</v>
       </c>
       <c r="E400" s="5" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
@@ -12177,7 +12177,7 @@
         <v>2025</v>
       </c>
       <c r="E401" s="5" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
@@ -12194,7 +12194,7 @@
         <v>2025</v>
       </c>
       <c r="E402" s="5" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.25">
@@ -12211,7 +12211,7 @@
         <v>2025</v>
       </c>
       <c r="E403" s="5" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
@@ -12228,7 +12228,7 @@
         <v>2025</v>
       </c>
       <c r="E404" s="5" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.25">
@@ -12245,15 +12245,15 @@
         <v>2025</v>
       </c>
       <c r="E405" s="5" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C406">
         <v>34</v>
@@ -12262,7 +12262,7 @@
         <v>2025</v>
       </c>
       <c r="E406" s="5" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.25">
@@ -12279,7 +12279,7 @@
         <v>2025</v>
       </c>
       <c r="E407" s="5" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.25">
@@ -12296,7 +12296,7 @@
         <v>2025</v>
       </c>
       <c r="E408" s="5" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.25">
@@ -12304,7 +12304,7 @@
         <v>334</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C409">
         <v>22</v>
@@ -12313,7 +12313,7 @@
         <v>2025</v>
       </c>
       <c r="E409" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.25">
@@ -12330,7 +12330,7 @@
         <v>2025</v>
       </c>
       <c r="E410" s="5" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
@@ -12347,7 +12347,7 @@
         <v>2025</v>
       </c>
       <c r="E411" s="5" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
@@ -12364,7 +12364,7 @@
         <v>2025</v>
       </c>
       <c r="E412" s="5" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
@@ -12381,7 +12381,7 @@
         <v>2025</v>
       </c>
       <c r="E413" s="5" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
@@ -12398,7 +12398,7 @@
         <v>2025</v>
       </c>
       <c r="E414" s="5" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.25">
@@ -12415,7 +12415,7 @@
         <v>2025</v>
       </c>
       <c r="E415" s="5" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.25">
@@ -12432,7 +12432,7 @@
         <v>2025</v>
       </c>
       <c r="E416" s="5" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
@@ -12449,7 +12449,7 @@
         <v>2025</v>
       </c>
       <c r="E417" s="5" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
@@ -12466,7 +12466,7 @@
         <v>2025</v>
       </c>
       <c r="E418" s="5" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
@@ -12483,7 +12483,7 @@
         <v>2025</v>
       </c>
       <c r="E419" s="5" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
@@ -12500,7 +12500,7 @@
         <v>2025</v>
       </c>
       <c r="E420" s="5" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
@@ -12517,7 +12517,7 @@
         <v>2025</v>
       </c>
       <c r="E421" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
@@ -12534,7 +12534,7 @@
         <v>2025</v>
       </c>
       <c r="E422" s="5" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.25">
@@ -12551,7 +12551,7 @@
         <v>2025</v>
       </c>
       <c r="E423" s="5" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
@@ -12568,12 +12568,12 @@
         <v>2025</v>
       </c>
       <c r="E424" s="5" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B425" s="1" t="s">
         <v>706</v>
@@ -12585,7 +12585,7 @@
         <v>2025</v>
       </c>
       <c r="E425" s="5" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
@@ -12602,7 +12602,7 @@
         <v>2025</v>
       </c>
       <c r="E426" s="5" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
@@ -12619,7 +12619,7 @@
         <v>2025</v>
       </c>
       <c r="E427" s="5" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
@@ -12636,12 +12636,12 @@
         <v>2025</v>
       </c>
       <c r="E428" s="5" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B429" s="1" t="s">
         <v>711</v>
@@ -12653,12 +12653,12 @@
         <v>2025</v>
       </c>
       <c r="E429" s="5" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B430" s="1" t="s">
         <v>713</v>
@@ -12670,7 +12670,7 @@
         <v>2025</v>
       </c>
       <c r="E430" s="5" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.25">
@@ -12687,7 +12687,7 @@
         <v>2025</v>
       </c>
       <c r="E431" s="5" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.25">
@@ -12704,7 +12704,7 @@
         <v>2025</v>
       </c>
       <c r="E432" s="5" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.25">
@@ -12721,12 +12721,12 @@
         <v>2025</v>
       </c>
       <c r="E433" s="5" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B434" s="1" t="s">
         <v>40</v>
@@ -12738,7 +12738,7 @@
         <v>2025</v>
       </c>
       <c r="E434" s="5" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.25">
@@ -12755,7 +12755,7 @@
         <v>2025</v>
       </c>
       <c r="E435" s="5" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.25">
@@ -12772,7 +12772,7 @@
         <v>2025</v>
       </c>
       <c r="E436" s="5" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
@@ -12789,7 +12789,7 @@
         <v>2025</v>
       </c>
       <c r="E437" s="5" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.25">
@@ -12806,12 +12806,12 @@
         <v>2025</v>
       </c>
       <c r="E438" s="5" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B439" s="1" t="s">
         <v>40</v>
@@ -12823,7 +12823,7 @@
         <v>2025</v>
       </c>
       <c r="E439" s="5" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.25">
@@ -12831,7 +12831,7 @@
         <v>343</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C440">
         <v>32</v>
@@ -12840,7 +12840,7 @@
         <v>2025</v>
       </c>
       <c r="E440" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.25">
@@ -12857,7 +12857,7 @@
         <v>2025</v>
       </c>
       <c r="E441" s="5" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.25">
@@ -12874,12 +12874,12 @@
         <v>2025</v>
       </c>
       <c r="E442" s="5" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B443" s="1" t="s">
         <v>710</v>
@@ -12891,7 +12891,7 @@
         <v>2025</v>
       </c>
       <c r="E443" s="5" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
@@ -12908,7 +12908,7 @@
         <v>2025</v>
       </c>
       <c r="E444" s="5" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
@@ -12916,7 +12916,7 @@
         <v>321</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C445">
         <v>7</v>
@@ -12925,7 +12925,7 @@
         <v>2025</v>
       </c>
       <c r="E445" s="5" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.25">
@@ -12942,7 +12942,7 @@
         <v>2025</v>
       </c>
       <c r="E446" s="5" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.25">
@@ -12959,7 +12959,7 @@
         <v>2025</v>
       </c>
       <c r="E447" s="5" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.25">
@@ -12976,7 +12976,7 @@
         <v>2025</v>
       </c>
       <c r="E448" s="5" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.25">
@@ -12993,7 +12993,7 @@
         <v>2025</v>
       </c>
       <c r="E449" s="5" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.25">
@@ -13010,7 +13010,7 @@
         <v>2025</v>
       </c>
       <c r="E450" s="5" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
@@ -13027,7 +13027,7 @@
         <v>2025</v>
       </c>
       <c r="E451" s="5" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.25">
@@ -13044,7 +13044,7 @@
         <v>2025</v>
       </c>
       <c r="E452" s="5" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
@@ -13061,7 +13061,7 @@
         <v>2025</v>
       </c>
       <c r="E453" s="5" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
@@ -13069,7 +13069,7 @@
         <v>320</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C454">
         <v>6</v>
@@ -13078,7 +13078,7 @@
         <v>2025</v>
       </c>
       <c r="E454" s="5" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.25">
@@ -13095,12 +13095,12 @@
         <v>2025</v>
       </c>
       <c r="E455" s="5" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B456" s="1" t="s">
         <v>712</v>
@@ -13112,7 +13112,7 @@
         <v>2025</v>
       </c>
       <c r="E456" s="5" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.25">
@@ -13129,7 +13129,7 @@
         <v>2025</v>
       </c>
       <c r="E457" s="5" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
@@ -13146,15 +13146,15 @@
         <v>2025</v>
       </c>
       <c r="E458" s="5" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C459">
         <v>25</v>
@@ -13163,7 +13163,7 @@
         <v>2025</v>
       </c>
       <c r="E459" s="5" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.25">
@@ -13180,7 +13180,7 @@
         <v>2025</v>
       </c>
       <c r="E460" s="5" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.25">
@@ -13197,12 +13197,12 @@
         <v>2025</v>
       </c>
       <c r="E461" s="5" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B462" s="1" t="s">
         <v>40</v>
@@ -13214,7 +13214,7 @@
         <v>2025</v>
       </c>
       <c r="E462" s="5" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
@@ -13231,7 +13231,7 @@
         <v>2025</v>
       </c>
       <c r="E463" s="5" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.25">
@@ -13248,7 +13248,7 @@
         <v>2025</v>
       </c>
       <c r="E464" s="5" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.25">
@@ -13265,7 +13265,7 @@
         <v>2025</v>
       </c>
       <c r="E465" s="5" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.25">
@@ -13282,7 +13282,7 @@
         <v>2025</v>
       </c>
       <c r="E466" s="5" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.25">
@@ -13299,7 +13299,7 @@
         <v>2025</v>
       </c>
       <c r="E467" s="5" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
@@ -13307,7 +13307,7 @@
         <v>333</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C468">
         <v>21</v>
@@ -13316,7 +13316,7 @@
         <v>2025</v>
       </c>
       <c r="E468" s="5" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.25">
@@ -13333,7 +13333,7 @@
         <v>2025</v>
       </c>
       <c r="E469" s="5" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.25">
@@ -13350,7 +13350,7 @@
         <v>2025</v>
       </c>
       <c r="E470" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.25">
@@ -13367,7 +13367,7 @@
         <v>2025</v>
       </c>
       <c r="E471" s="5" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.25">
@@ -13384,7 +13384,7 @@
         <v>2025</v>
       </c>
       <c r="E472" s="5" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.25">
@@ -13401,7 +13401,7 @@
         <v>2025</v>
       </c>
       <c r="E473" s="5" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.25">
@@ -13418,7 +13418,7 @@
         <v>2025</v>
       </c>
       <c r="E474" s="5" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.25">
@@ -13435,7 +13435,7 @@
         <v>2025</v>
       </c>
       <c r="E475" s="5" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.25">
@@ -13452,7 +13452,7 @@
         <v>2025</v>
       </c>
       <c r="E476" s="5" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.25">
@@ -13469,7 +13469,7 @@
         <v>2025</v>
       </c>
       <c r="E477" s="5" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.25">
@@ -13486,12 +13486,12 @@
         <v>2025</v>
       </c>
       <c r="E478" s="5" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B479" s="1" t="s">
         <v>717</v>
@@ -13503,7 +13503,7 @@
         <v>2025</v>
       </c>
       <c r="E479" s="5" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.25">
@@ -13520,7 +13520,7 @@
         <v>2025</v>
       </c>
       <c r="E480" s="5" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.25">
@@ -13537,7 +13537,7 @@
         <v>2025</v>
       </c>
       <c r="E481" s="5" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.25">
@@ -13554,7 +13554,7 @@
         <v>2025</v>
       </c>
       <c r="E482" s="5" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.25">
@@ -13571,7 +13571,7 @@
         <v>2025</v>
       </c>
       <c r="E483" s="5" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.25">
@@ -13588,7 +13588,7 @@
         <v>2025</v>
       </c>
       <c r="E484" s="5" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.25">
@@ -13605,12 +13605,12 @@
         <v>2025</v>
       </c>
       <c r="E485" s="5" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B486" s="1" t="s">
         <v>708</v>
@@ -13622,7 +13622,7 @@
         <v>2025</v>
       </c>
       <c r="E486" s="5" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.25">
@@ -13639,12 +13639,12 @@
         <v>2025</v>
       </c>
       <c r="E487" s="5" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B488" s="1" t="s">
         <v>716</v>
@@ -13656,7 +13656,7 @@
         <v>2025</v>
       </c>
       <c r="E488" s="5" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.25">
@@ -13673,7 +13673,7 @@
         <v>2025</v>
       </c>
       <c r="E489" s="5" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.25">
@@ -13690,7 +13690,7 @@
         <v>2025</v>
       </c>
       <c r="E490" s="5" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.25">
@@ -13707,7 +13707,7 @@
         <v>2025</v>
       </c>
       <c r="E491" s="5" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.25">
@@ -13715,7 +13715,7 @@
         <v>346</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C492">
         <v>36</v>
@@ -13724,12 +13724,12 @@
         <v>2025</v>
       </c>
       <c r="E492" s="5" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B493" s="1" t="s">
         <v>706</v>
@@ -13741,7 +13741,7 @@
         <v>2025</v>
       </c>
       <c r="E493" s="5" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.25">
@@ -13758,7 +13758,7 @@
         <v>2025</v>
       </c>
       <c r="E494" s="5" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.25">
@@ -13775,7 +13775,7 @@
         <v>2025</v>
       </c>
       <c r="E495" s="5" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.25">
@@ -13792,12 +13792,12 @@
         <v>2025</v>
       </c>
       <c r="E496" s="5" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B497" s="1" t="s">
         <v>709</v>
@@ -13809,7 +13809,7 @@
         <v>2025</v>
       </c>
       <c r="E497" s="5" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.25">
@@ -13826,7 +13826,7 @@
         <v>2025</v>
       </c>
       <c r="E498" s="5" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.25">
@@ -13843,7 +13843,7 @@
         <v>2025</v>
       </c>
       <c r="E499" s="5" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.25">
@@ -13860,7 +13860,7 @@
         <v>2025</v>
       </c>
       <c r="E500" s="5" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.25">
@@ -13877,7 +13877,7 @@
         <v>2025</v>
       </c>
       <c r="E501" s="5" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.25">
@@ -13894,7 +13894,7 @@
         <v>2025</v>
       </c>
       <c r="E502" s="5" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.25">
@@ -13911,7 +13911,7 @@
         <v>2025</v>
       </c>
       <c r="E503" s="5" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.25">
@@ -13928,7 +13928,7 @@
         <v>2025</v>
       </c>
       <c r="E504" s="5" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.25">
@@ -13945,7 +13945,7 @@
         <v>2025</v>
       </c>
       <c r="E505" s="5" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.25">
@@ -13962,7 +13962,7 @@
         <v>2025</v>
       </c>
       <c r="E506" s="5" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.25">
@@ -13979,7 +13979,7 @@
         <v>2025</v>
       </c>
       <c r="E507" s="5" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.25">
@@ -13996,7 +13996,7 @@
         <v>2025</v>
       </c>
       <c r="E508" s="5" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.25">
@@ -14013,7 +14013,7 @@
         <v>2025</v>
       </c>
       <c r="E509" s="5" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.25">
@@ -14030,7 +14030,7 @@
         <v>2025</v>
       </c>
       <c r="E510" s="5" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.25">
@@ -14047,7 +14047,7 @@
         <v>2025</v>
       </c>
       <c r="E511" s="5" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.25">
@@ -14064,7 +14064,7 @@
         <v>2025</v>
       </c>
       <c r="E512" s="5" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.25">
@@ -14081,7 +14081,7 @@
         <v>2025</v>
       </c>
       <c r="E513" s="5" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.25">
@@ -14098,7 +14098,7 @@
         <v>2025</v>
       </c>
       <c r="E514" s="5" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.25">
@@ -14115,7 +14115,7 @@
         <v>2025</v>
       </c>
       <c r="E515" s="5" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.25">
@@ -14132,7 +14132,7 @@
         <v>2025</v>
       </c>
       <c r="E516" s="5" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.25">
@@ -14149,7 +14149,7 @@
         <v>2025</v>
       </c>
       <c r="E517" s="5" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.25">
@@ -14166,7 +14166,7 @@
         <v>2025</v>
       </c>
       <c r="E518" s="5" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.25">
@@ -14183,7 +14183,7 @@
         <v>2025</v>
       </c>
       <c r="E519" s="5" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.25">
@@ -14200,7 +14200,7 @@
         <v>2025</v>
       </c>
       <c r="E520" s="5" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="521" spans="1:5" x14ac:dyDescent="0.25">
@@ -14217,12 +14217,12 @@
         <v>2025</v>
       </c>
       <c r="E521" s="5" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B522" s="1" t="s">
         <v>710</v>
@@ -14234,7 +14234,7 @@
         <v>2025</v>
       </c>
       <c r="E522" s="5" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="523" spans="1:5" x14ac:dyDescent="0.25">
@@ -14251,7 +14251,7 @@
         <v>2025</v>
       </c>
       <c r="E523" s="5" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="524" spans="1:5" x14ac:dyDescent="0.25">
@@ -14268,7 +14268,7 @@
         <v>2025</v>
       </c>
       <c r="E524" s="5" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.25">
@@ -14285,7 +14285,7 @@
         <v>2025</v>
       </c>
       <c r="E525" s="5" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.25">
@@ -14302,12 +14302,12 @@
         <v>2025</v>
       </c>
       <c r="E526" s="5" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B527" s="1" t="s">
         <v>713</v>
@@ -14319,7 +14319,7 @@
         <v>2025</v>
       </c>
       <c r="E527" s="5" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.25">
@@ -14336,7 +14336,7 @@
         <v>2025</v>
       </c>
       <c r="E528" s="5" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.25">
@@ -14353,12 +14353,12 @@
         <v>2025</v>
       </c>
       <c r="E529" s="5" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B530" s="1" t="s">
         <v>40</v>
@@ -14370,7 +14370,7 @@
         <v>2025</v>
       </c>
       <c r="E530" s="5" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.25">
@@ -14387,7 +14387,7 @@
         <v>2025</v>
       </c>
       <c r="E531" s="5" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.25">
@@ -14404,7 +14404,7 @@
         <v>2025</v>
       </c>
       <c r="E532" s="5" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.25">
@@ -14421,7 +14421,7 @@
         <v>2025</v>
       </c>
       <c r="E533" s="5" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.25">
@@ -14438,7 +14438,7 @@
         <v>2025</v>
       </c>
       <c r="E534" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.25">
@@ -14455,7 +14455,7 @@
         <v>2025</v>
       </c>
       <c r="E535" s="5" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.25">
@@ -14472,7 +14472,7 @@
         <v>2025</v>
       </c>
       <c r="E536" s="5" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="537" spans="1:5" x14ac:dyDescent="0.25">
@@ -14489,7 +14489,7 @@
         <v>2025</v>
       </c>
       <c r="E537" s="5" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.25">
@@ -14506,7 +14506,7 @@
         <v>2025</v>
       </c>
       <c r="E538" s="5" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.25">
@@ -14523,7 +14523,7 @@
         <v>2025</v>
       </c>
       <c r="E539" s="5" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.25">
@@ -14540,7 +14540,7 @@
         <v>2025</v>
       </c>
       <c r="E540" s="5" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.25">
@@ -14557,7 +14557,7 @@
         <v>2025</v>
       </c>
       <c r="E541" s="5" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.25">
@@ -14574,7 +14574,7 @@
         <v>2025</v>
       </c>
       <c r="E542" s="5" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.25">
@@ -14591,7 +14591,7 @@
         <v>2025</v>
       </c>
       <c r="E543" s="5" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.25">
@@ -14608,7 +14608,7 @@
         <v>2025</v>
       </c>
       <c r="E544" s="5" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.25">
@@ -14616,7 +14616,7 @@
         <v>345</v>
       </c>
       <c r="B545" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C545">
         <v>35</v>
@@ -14625,7 +14625,7 @@
         <v>2025</v>
       </c>
       <c r="E545" s="5" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.25">
@@ -14642,7 +14642,7 @@
         <v>2025</v>
       </c>
       <c r="E546" s="5" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.25">
@@ -14659,7 +14659,7 @@
         <v>2025</v>
       </c>
       <c r="E547" s="5" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.25">
@@ -14676,7 +14676,7 @@
         <v>2025</v>
       </c>
       <c r="E548" s="5" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="549" spans="1:5" x14ac:dyDescent="0.25">
@@ -14693,7 +14693,7 @@
         <v>2025</v>
       </c>
       <c r="E549" s="5" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.25">
@@ -14710,7 +14710,7 @@
         <v>2025</v>
       </c>
       <c r="E550" s="5" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.25">
@@ -14727,7 +14727,7 @@
         <v>2025</v>
       </c>
       <c r="E551" s="5" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.25">
@@ -14744,7 +14744,7 @@
         <v>2025</v>
       </c>
       <c r="E552" s="5" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.25">
@@ -14761,7 +14761,7 @@
         <v>2025</v>
       </c>
       <c r="E553" s="5" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.25">
@@ -14778,12 +14778,12 @@
         <v>2025</v>
       </c>
       <c r="E554" s="5" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="555" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B555" s="1" t="s">
         <v>707</v>
@@ -14795,7 +14795,7 @@
         <v>2025</v>
       </c>
       <c r="E555" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.25">
@@ -14812,12 +14812,12 @@
         <v>2025</v>
       </c>
       <c r="E556" s="5" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B557" s="1" t="s">
         <v>711</v>
@@ -14829,12 +14829,12 @@
         <v>2025</v>
       </c>
       <c r="E557" s="5" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B558" s="1" t="s">
         <v>722</v>
@@ -14846,7 +14846,7 @@
         <v>2025</v>
       </c>
       <c r="E558" s="5" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.25">
@@ -14863,7 +14863,7 @@
         <v>2025</v>
       </c>
       <c r="E559" s="5" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.25">
@@ -14880,7 +14880,7 @@
         <v>2025</v>
       </c>
       <c r="E560" s="5" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.25">
@@ -14897,7 +14897,7 @@
         <v>2025</v>
       </c>
       <c r="E561" s="5" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="562" spans="1:5" x14ac:dyDescent="0.25">
@@ -14914,7 +14914,7 @@
         <v>2025</v>
       </c>
       <c r="E562" s="5" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.25">
@@ -14931,7 +14931,7 @@
         <v>2025</v>
       </c>
       <c r="E563" s="5" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.25">
@@ -14948,7 +14948,7 @@
         <v>2025</v>
       </c>
       <c r="E564" s="5" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.25">
@@ -14965,7 +14965,7 @@
         <v>2025</v>
       </c>
       <c r="E565" s="5" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.25">
@@ -14982,7 +14982,7 @@
         <v>2025</v>
       </c>
       <c r="E566" s="5" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="567" spans="1:5" x14ac:dyDescent="0.25">
@@ -14999,7 +14999,7 @@
         <v>2025</v>
       </c>
       <c r="E567" s="5" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.25">
@@ -15016,7 +15016,7 @@
         <v>2025</v>
       </c>
       <c r="E568" s="5" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.25">
@@ -15033,7 +15033,7 @@
         <v>2025</v>
       </c>
       <c r="E569" s="5" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="570" spans="1:5" x14ac:dyDescent="0.25">
@@ -15050,12 +15050,12 @@
         <v>2025</v>
       </c>
       <c r="E570" s="5" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="571" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B571" s="1" t="s">
         <v>707</v>
@@ -15067,7 +15067,7 @@
         <v>2025</v>
       </c>
       <c r="E571" s="5" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.25">
@@ -15084,7 +15084,7 @@
         <v>2025</v>
       </c>
       <c r="E572" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="573" spans="1:5" x14ac:dyDescent="0.25">
@@ -15092,7 +15092,7 @@
         <v>351</v>
       </c>
       <c r="B573" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C573">
         <v>42</v>
@@ -15101,7 +15101,7 @@
         <v>2025</v>
       </c>
       <c r="E573" s="5" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="574" spans="1:5" x14ac:dyDescent="0.25">
@@ -15118,7 +15118,7 @@
         <v>2025</v>
       </c>
       <c r="E574" s="5" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="575" spans="1:5" x14ac:dyDescent="0.25">
@@ -15135,7 +15135,7 @@
         <v>2025</v>
       </c>
       <c r="E575" s="5" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.25">
@@ -15152,7 +15152,7 @@
         <v>2025</v>
       </c>
       <c r="E576" s="5" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.25">
@@ -15169,7 +15169,7 @@
         <v>2025</v>
       </c>
       <c r="E577" s="5" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="578" spans="1:5" x14ac:dyDescent="0.25">
@@ -15186,7 +15186,7 @@
         <v>2025</v>
       </c>
       <c r="E578" s="5" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="579" spans="1:5" x14ac:dyDescent="0.25">
@@ -15203,7 +15203,7 @@
         <v>2025</v>
       </c>
       <c r="E579" s="5" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
@@ -15220,7 +15220,7 @@
         <v>2025</v>
       </c>
       <c r="E580" s="5" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.25">
@@ -15237,7 +15237,7 @@
         <v>2025</v>
       </c>
       <c r="E581" s="5" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="582" spans="1:5" x14ac:dyDescent="0.25">
@@ -15254,7 +15254,7 @@
         <v>2025</v>
       </c>
       <c r="E582" s="5" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="583" spans="1:5" x14ac:dyDescent="0.25">
@@ -15271,7 +15271,7 @@
         <v>2025</v>
       </c>
       <c r="E583" s="5" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="584" spans="1:5" x14ac:dyDescent="0.25">
@@ -15288,7 +15288,7 @@
         <v>2025</v>
       </c>
       <c r="E584" s="5" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="585" spans="1:5" x14ac:dyDescent="0.25">
@@ -15305,7 +15305,7 @@
         <v>2025</v>
       </c>
       <c r="E585" s="5" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="586" spans="1:5" x14ac:dyDescent="0.25">
@@ -15322,7 +15322,7 @@
         <v>2025</v>
       </c>
       <c r="E586" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="587" spans="1:5" x14ac:dyDescent="0.25">
@@ -15339,7 +15339,7 @@
         <v>2025</v>
       </c>
       <c r="E587" s="5" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="588" spans="1:5" x14ac:dyDescent="0.25">
@@ -15347,7 +15347,7 @@
         <v>350</v>
       </c>
       <c r="B588" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C588">
         <v>41</v>
@@ -15356,7 +15356,7 @@
         <v>2025</v>
       </c>
       <c r="E588" s="5" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="589" spans="1:5" x14ac:dyDescent="0.25">
@@ -15373,7 +15373,7 @@
         <v>2025</v>
       </c>
       <c r="E589" s="5" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="590" spans="1:5" x14ac:dyDescent="0.25">
@@ -15390,7 +15390,7 @@
         <v>2025</v>
       </c>
       <c r="E590" s="5" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="591" spans="1:5" x14ac:dyDescent="0.25">
@@ -15407,7 +15407,7 @@
         <v>2025</v>
       </c>
       <c r="E591" s="5" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="592" spans="1:5" x14ac:dyDescent="0.25">
@@ -15424,7 +15424,7 @@
         <v>2025</v>
       </c>
       <c r="E592" s="5" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="593" spans="1:5" x14ac:dyDescent="0.25">
@@ -15441,7 +15441,7 @@
         <v>2025</v>
       </c>
       <c r="E593" s="5" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="594" spans="1:5" x14ac:dyDescent="0.25">
@@ -15458,7 +15458,7 @@
         <v>2025</v>
       </c>
       <c r="E594" s="5" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.25">
@@ -15475,7 +15475,7 @@
         <v>2025</v>
       </c>
       <c r="E595" s="5" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.25">
@@ -15492,7 +15492,7 @@
         <v>2025</v>
       </c>
       <c r="E596" s="5" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.25">
@@ -15509,7 +15509,7 @@
         <v>2025</v>
       </c>
       <c r="E597" s="5" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="598" spans="1:5" x14ac:dyDescent="0.25">
@@ -15526,12 +15526,12 @@
         <v>2025</v>
       </c>
       <c r="E598" s="5" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B599" s="1" t="s">
         <v>707</v>
@@ -15543,7 +15543,7 @@
         <v>2025</v>
       </c>
       <c r="E599" s="5" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="600" spans="1:5" x14ac:dyDescent="0.25">
@@ -15560,12 +15560,12 @@
         <v>2025</v>
       </c>
       <c r="E600" s="5" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="601" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B601" s="1" t="s">
         <v>159</v>
@@ -15577,7 +15577,7 @@
         <v>2025</v>
       </c>
       <c r="E601" s="5" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="602" spans="1:5" x14ac:dyDescent="0.25">
@@ -15594,7 +15594,7 @@
         <v>2025</v>
       </c>
       <c r="E602" s="5" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="603" spans="1:5" x14ac:dyDescent="0.25">
@@ -15611,7 +15611,7 @@
         <v>2025</v>
       </c>
       <c r="E603" s="5" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="604" spans="1:5" x14ac:dyDescent="0.25">
@@ -15628,7 +15628,7 @@
         <v>2025</v>
       </c>
       <c r="E604" s="5" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="605" spans="1:5" x14ac:dyDescent="0.25">
@@ -15645,7 +15645,7 @@
         <v>2025</v>
       </c>
       <c r="E605" s="5" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="606" spans="1:5" x14ac:dyDescent="0.25">
@@ -15662,7 +15662,7 @@
         <v>2025</v>
       </c>
       <c r="E606" s="5" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="607" spans="1:5" x14ac:dyDescent="0.25">
@@ -15679,12 +15679,12 @@
         <v>2025</v>
       </c>
       <c r="E607" s="5" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="608" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B608" s="1" t="s">
         <v>710</v>
@@ -15696,7 +15696,7 @@
         <v>2025</v>
       </c>
       <c r="E608" s="5" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="609" spans="1:5" x14ac:dyDescent="0.25">
@@ -15704,7 +15704,7 @@
         <v>325</v>
       </c>
       <c r="B609" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C609">
         <v>13</v>
@@ -15713,7 +15713,7 @@
         <v>2025</v>
       </c>
       <c r="E609" s="5" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="610" spans="1:5" x14ac:dyDescent="0.25">
@@ -15730,7 +15730,7 @@
         <v>2025</v>
       </c>
       <c r="E610" s="5" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="611" spans="1:5" x14ac:dyDescent="0.25">
@@ -15747,7 +15747,7 @@
         <v>2025</v>
       </c>
       <c r="E611" s="5" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="612" spans="1:5" x14ac:dyDescent="0.25">
@@ -15764,12 +15764,12 @@
         <v>2025</v>
       </c>
       <c r="E612" s="5" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="613" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B613" s="1" t="s">
         <v>120</v>
@@ -15781,7 +15781,7 @@
         <v>2025</v>
       </c>
       <c r="E613" s="5" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="614" spans="1:5" x14ac:dyDescent="0.25">
@@ -15798,7 +15798,7 @@
         <v>2025</v>
       </c>
       <c r="E614" s="5" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="615" spans="1:5" x14ac:dyDescent="0.25">
@@ -15815,7 +15815,7 @@
         <v>2025</v>
       </c>
       <c r="E615" s="5" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="616" spans="1:5" x14ac:dyDescent="0.25">
@@ -15832,12 +15832,12 @@
         <v>2025</v>
       </c>
       <c r="E616" s="5" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="617" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B617" s="1" t="s">
         <v>721</v>
@@ -15849,7 +15849,7 @@
         <v>2025</v>
       </c>
       <c r="E617" s="5" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="618" spans="1:5" x14ac:dyDescent="0.25">
@@ -15866,7 +15866,7 @@
         <v>2025</v>
       </c>
       <c r="E618" s="5" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="619" spans="1:5" x14ac:dyDescent="0.25">
@@ -15883,7 +15883,7 @@
         <v>2025</v>
       </c>
       <c r="E619" s="5" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="620" spans="1:5" x14ac:dyDescent="0.25">
@@ -15900,7 +15900,7 @@
         <v>2025</v>
       </c>
       <c r="E620" s="5" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="621" spans="1:5" x14ac:dyDescent="0.25">
@@ -15917,7 +15917,7 @@
         <v>2025</v>
       </c>
       <c r="E621" s="5" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="622" spans="1:5" x14ac:dyDescent="0.25">
@@ -15934,7 +15934,7 @@
         <v>2025</v>
       </c>
       <c r="E622" s="5" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="623" spans="1:5" x14ac:dyDescent="0.25">
@@ -15951,7 +15951,7 @@
         <v>2025</v>
       </c>
       <c r="E623" s="5" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="624" spans="1:5" x14ac:dyDescent="0.25">
@@ -15968,7 +15968,7 @@
         <v>2025</v>
       </c>
       <c r="E624" s="5" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="625" spans="1:5" x14ac:dyDescent="0.25">
@@ -15985,7 +15985,7 @@
         <v>2025</v>
       </c>
       <c r="E625" s="5" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="626" spans="1:5" x14ac:dyDescent="0.25">
@@ -16002,7 +16002,7 @@
         <v>2025</v>
       </c>
       <c r="E626" s="5" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="627" spans="1:5" x14ac:dyDescent="0.25">
@@ -16019,7 +16019,7 @@
         <v>2025</v>
       </c>
       <c r="E627" s="5" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="628" spans="1:5" x14ac:dyDescent="0.25">
@@ -16036,7 +16036,7 @@
         <v>2025</v>
       </c>
       <c r="E628" s="5" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.25">
@@ -16053,7 +16053,7 @@
         <v>2025</v>
       </c>
       <c r="E629" s="5" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="630" spans="1:5" x14ac:dyDescent="0.25">
@@ -16070,7 +16070,7 @@
         <v>2025</v>
       </c>
       <c r="E630" s="5" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="631" spans="1:5" x14ac:dyDescent="0.25">
@@ -16087,7 +16087,7 @@
         <v>2025</v>
       </c>
       <c r="E631" s="5" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.25">
@@ -16095,7 +16095,7 @@
         <v>323</v>
       </c>
       <c r="B632" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C632">
         <v>11</v>
@@ -16104,12 +16104,12 @@
         <v>2025</v>
       </c>
       <c r="E632" s="5" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B633" s="1" t="s">
         <v>707</v>
@@ -16121,7 +16121,7 @@
         <v>2025</v>
       </c>
       <c r="E633" s="5" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="634" spans="1:5" x14ac:dyDescent="0.25">
@@ -16138,7 +16138,7 @@
         <v>2025</v>
       </c>
       <c r="E634" s="5" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="635" spans="1:5" x14ac:dyDescent="0.25">
@@ -16155,7 +16155,7 @@
         <v>2025</v>
       </c>
       <c r="E635" s="5" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.25">
@@ -16172,7 +16172,7 @@
         <v>2025</v>
       </c>
       <c r="E636" s="5" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="637" spans="1:5" x14ac:dyDescent="0.25">
@@ -16189,7 +16189,7 @@
         <v>2025</v>
       </c>
       <c r="E637" s="5" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.25">
@@ -16206,7 +16206,7 @@
         <v>2025</v>
       </c>
       <c r="E638" s="5" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="639" spans="1:5" x14ac:dyDescent="0.25">
@@ -16223,7 +16223,7 @@
         <v>2025</v>
       </c>
       <c r="E639" s="5" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="640" spans="1:5" x14ac:dyDescent="0.25">
@@ -16240,7 +16240,7 @@
         <v>2025</v>
       </c>
       <c r="E640" s="5" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="641" spans="1:5" x14ac:dyDescent="0.25">
@@ -16257,7 +16257,7 @@
         <v>2025</v>
       </c>
       <c r="E641" s="5" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="642" spans="1:5" x14ac:dyDescent="0.25">
@@ -16274,7 +16274,7 @@
         <v>2025</v>
       </c>
       <c r="E642" s="5" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="643" spans="1:5" x14ac:dyDescent="0.25">
@@ -16291,7 +16291,7 @@
         <v>2025</v>
       </c>
       <c r="E643" s="5" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="644" spans="1:5" x14ac:dyDescent="0.25">
@@ -16308,7 +16308,7 @@
         <v>2025</v>
       </c>
       <c r="E644" s="5" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="645" spans="1:5" x14ac:dyDescent="0.25">
@@ -16325,7 +16325,7 @@
         <v>2025</v>
       </c>
       <c r="E645" s="5" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="646" spans="1:5" x14ac:dyDescent="0.25">
@@ -16342,7 +16342,7 @@
         <v>2025</v>
       </c>
       <c r="E646" s="5" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.25">
@@ -16359,7 +16359,7 @@
         <v>2025</v>
       </c>
       <c r="E647" s="5" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="648" spans="1:5" x14ac:dyDescent="0.25">
@@ -16376,7 +16376,7 @@
         <v>2025</v>
       </c>
       <c r="E648" s="5" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="649" spans="1:5" x14ac:dyDescent="0.25">
@@ -16393,7 +16393,7 @@
         <v>2025</v>
       </c>
       <c r="E649" s="5" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.25">
@@ -16410,7 +16410,7 @@
         <v>2025</v>
       </c>
       <c r="E650" s="5" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="651" spans="1:5" x14ac:dyDescent="0.25">
@@ -16427,12 +16427,12 @@
         <v>2025</v>
       </c>
       <c r="E651" s="5" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="652" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B652" s="1" t="s">
         <v>715</v>
@@ -16444,7 +16444,7 @@
         <v>2025</v>
       </c>
       <c r="E652" s="5" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="653" spans="1:5" x14ac:dyDescent="0.25">
@@ -16461,12 +16461,12 @@
         <v>2025</v>
       </c>
       <c r="E653" s="5" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="654" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B654" s="1" t="s">
         <v>712</v>
@@ -16478,7 +16478,7 @@
         <v>2025</v>
       </c>
       <c r="E654" s="5" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="655" spans="1:5" x14ac:dyDescent="0.25">
@@ -16495,7 +16495,7 @@
         <v>2025</v>
       </c>
       <c r="E655" s="5" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="656" spans="1:5" x14ac:dyDescent="0.25">
@@ -16512,7 +16512,7 @@
         <v>2025</v>
       </c>
       <c r="E656" s="5" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="657" spans="1:5" x14ac:dyDescent="0.25">
@@ -16529,7 +16529,7 @@
         <v>2025</v>
       </c>
       <c r="E657" s="5" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="658" spans="1:5" x14ac:dyDescent="0.25">
@@ -16537,7 +16537,7 @@
         <v>322</v>
       </c>
       <c r="B658" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C658">
         <v>9</v>
@@ -16546,12 +16546,12 @@
         <v>2025</v>
       </c>
       <c r="E658" s="5" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="659" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B659" s="1" t="s">
         <v>712</v>
@@ -16563,7 +16563,7 @@
         <v>2025</v>
       </c>
       <c r="E659" s="5" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="660" spans="1:5" x14ac:dyDescent="0.25">
@@ -16580,7 +16580,7 @@
         <v>2025</v>
       </c>
       <c r="E660" s="5" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="661" spans="1:5" x14ac:dyDescent="0.25">
@@ -16597,7 +16597,7 @@
         <v>2025</v>
       </c>
       <c r="E661" s="5" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="662" spans="1:5" x14ac:dyDescent="0.25">
@@ -16614,7 +16614,7 @@
         <v>2025</v>
       </c>
       <c r="E662" s="5" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="663" spans="1:5" x14ac:dyDescent="0.25">
@@ -16631,7 +16631,7 @@
         <v>2025</v>
       </c>
       <c r="E663" s="5" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="664" spans="1:5" x14ac:dyDescent="0.25">
@@ -16648,7 +16648,7 @@
         <v>2025</v>
       </c>
       <c r="E664" s="5" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="665" spans="1:5" x14ac:dyDescent="0.25">
@@ -16665,7 +16665,7 @@
         <v>2025</v>
       </c>
       <c r="E665" s="5" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="666" spans="1:5" x14ac:dyDescent="0.25">
@@ -16682,7 +16682,7 @@
         <v>2025</v>
       </c>
       <c r="E666" s="5" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="667" spans="1:5" x14ac:dyDescent="0.25">
@@ -16699,7 +16699,7 @@
         <v>2025</v>
       </c>
       <c r="E667" s="5" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="668" spans="1:5" x14ac:dyDescent="0.25">
@@ -16716,7 +16716,7 @@
         <v>2025</v>
       </c>
       <c r="E668" s="5" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="669" spans="1:5" x14ac:dyDescent="0.25">
@@ -16733,7 +16733,7 @@
         <v>2025</v>
       </c>
       <c r="E669" s="5" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="670" spans="1:5" x14ac:dyDescent="0.25">
@@ -16750,7 +16750,7 @@
         <v>2025</v>
       </c>
       <c r="E670" s="5" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="671" spans="1:5" x14ac:dyDescent="0.25">
@@ -16767,7 +16767,7 @@
         <v>2025</v>
       </c>
       <c r="E671" s="5" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="672" spans="1:5" x14ac:dyDescent="0.25">
@@ -16784,12 +16784,12 @@
         <v>2025</v>
       </c>
       <c r="E672" s="5" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="673" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B673" s="1" t="s">
         <v>721</v>
@@ -16801,7 +16801,7 @@
         <v>2025</v>
       </c>
       <c r="E673" s="5" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="674" spans="1:5" x14ac:dyDescent="0.25">
@@ -16818,12 +16818,12 @@
         <v>2025</v>
       </c>
       <c r="E674" s="5" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="675" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B675" s="1" t="s">
         <v>120</v>
@@ -16835,7 +16835,7 @@
         <v>2025</v>
       </c>
       <c r="E675" s="5" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="676" spans="1:5" x14ac:dyDescent="0.25">
@@ -16852,7 +16852,7 @@
         <v>2025</v>
       </c>
       <c r="E676" s="5" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="677" spans="1:5" x14ac:dyDescent="0.25">
@@ -16869,7 +16869,7 @@
         <v>2025</v>
       </c>
       <c r="E677" s="5" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="678" spans="1:5" x14ac:dyDescent="0.25">
@@ -16886,12 +16886,12 @@
         <v>2025</v>
       </c>
       <c r="E678" s="5" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="679" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B679" s="1" t="s">
         <v>709</v>
@@ -16903,7 +16903,7 @@
         <v>2025</v>
       </c>
       <c r="E679" s="5" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="680" spans="1:5" x14ac:dyDescent="0.25">
@@ -16920,7 +16920,7 @@
         <v>2025</v>
       </c>
       <c r="E680" s="5" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="681" spans="1:5" x14ac:dyDescent="0.25">
@@ -16937,7 +16937,7 @@
         <v>2025</v>
       </c>
       <c r="E681" s="5" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="682" spans="1:5" x14ac:dyDescent="0.25">
@@ -16954,7 +16954,7 @@
         <v>2025</v>
       </c>
       <c r="E682" s="5" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="683" spans="1:5" x14ac:dyDescent="0.25">
@@ -16971,7 +16971,7 @@
         <v>2025</v>
       </c>
       <c r="E683" s="5" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="684" spans="1:5" x14ac:dyDescent="0.25">
@@ -16988,7 +16988,7 @@
         <v>2025</v>
       </c>
       <c r="E684" s="5" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="685" spans="1:5" x14ac:dyDescent="0.25">
@@ -16996,7 +16996,7 @@
         <v>327</v>
       </c>
       <c r="B685" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C685">
         <v>15</v>
@@ -17005,7 +17005,7 @@
         <v>2025</v>
       </c>
       <c r="E685" s="5" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="686" spans="1:5" x14ac:dyDescent="0.25">
@@ -17022,7 +17022,7 @@
         <v>2025</v>
       </c>
       <c r="E686" s="5" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="687" spans="1:5" x14ac:dyDescent="0.25">
@@ -17039,7 +17039,7 @@
         <v>2025</v>
       </c>
       <c r="E687" s="5" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="688" spans="1:5" x14ac:dyDescent="0.25">
@@ -17056,7 +17056,7 @@
         <v>2025</v>
       </c>
       <c r="E688" s="5" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="689" spans="1:5" x14ac:dyDescent="0.25">
@@ -17073,7 +17073,7 @@
         <v>2025</v>
       </c>
       <c r="E689" s="5" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="690" spans="1:5" x14ac:dyDescent="0.25">
@@ -17090,12 +17090,12 @@
         <v>2025</v>
       </c>
       <c r="E690" s="5" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="691" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B691" s="1" t="s">
         <v>709</v>
@@ -17107,7 +17107,7 @@
         <v>2025</v>
       </c>
       <c r="E691" s="5" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="692" spans="1:5" x14ac:dyDescent="0.25">
@@ -17124,12 +17124,12 @@
         <v>2025</v>
       </c>
       <c r="E692" s="5" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="693" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B693" s="1" t="s">
         <v>708</v>
@@ -17141,7 +17141,7 @@
         <v>2025</v>
       </c>
       <c r="E693" s="5" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="694" spans="1:5" x14ac:dyDescent="0.25">
@@ -17158,7 +17158,7 @@
         <v>2025</v>
       </c>
       <c r="E694" s="5" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="695" spans="1:5" x14ac:dyDescent="0.25">
@@ -17175,7 +17175,7 @@
         <v>2025</v>
       </c>
       <c r="E695" s="5" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="696" spans="1:5" x14ac:dyDescent="0.25">
@@ -17192,7 +17192,7 @@
         <v>2025</v>
       </c>
       <c r="E696" s="5" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="697" spans="1:5" x14ac:dyDescent="0.25">
@@ -17209,7 +17209,7 @@
         <v>2025</v>
       </c>
       <c r="E697" s="5" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="698" spans="1:5" x14ac:dyDescent="0.25">
@@ -17226,7 +17226,7 @@
         <v>2025</v>
       </c>
       <c r="E698" s="5" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="699" spans="1:5" x14ac:dyDescent="0.25">
@@ -17243,7 +17243,7 @@
         <v>2025</v>
       </c>
       <c r="E699" s="5" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="700" spans="1:5" x14ac:dyDescent="0.25">
@@ -17260,7 +17260,7 @@
         <v>2025</v>
       </c>
       <c r="E700" s="5" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="701" spans="1:5" x14ac:dyDescent="0.25">
@@ -17277,7 +17277,7 @@
         <v>2025</v>
       </c>
       <c r="E701" s="5" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="702" spans="1:5" x14ac:dyDescent="0.25">
@@ -17294,7 +17294,7 @@
         <v>2025</v>
       </c>
       <c r="E702" s="5" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="703" spans="1:5" x14ac:dyDescent="0.25">
@@ -17302,7 +17302,7 @@
         <v>317</v>
       </c>
       <c r="B703" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C703">
         <v>3</v>
@@ -17311,7 +17311,7 @@
         <v>2025</v>
       </c>
       <c r="E703" s="5" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="704" spans="1:5" x14ac:dyDescent="0.25">
@@ -17328,7 +17328,7 @@
         <v>2025</v>
       </c>
       <c r="E704" s="5" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="705" spans="1:5" x14ac:dyDescent="0.25">
@@ -17345,12 +17345,12 @@
         <v>2025</v>
       </c>
       <c r="E705" s="5" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="706" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B706" s="1" t="s">
         <v>710</v>
@@ -17362,7 +17362,7 @@
         <v>2025</v>
       </c>
       <c r="E706" s="5" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="707" spans="1:5" x14ac:dyDescent="0.25">
@@ -17379,7 +17379,7 @@
         <v>2025</v>
       </c>
       <c r="E707" s="5" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="708" spans="1:5" x14ac:dyDescent="0.25">
@@ -17396,12 +17396,12 @@
         <v>2025</v>
       </c>
       <c r="E708" s="5" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="709" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B709" s="1" t="s">
         <v>717</v>
@@ -17413,7 +17413,7 @@
         <v>2025</v>
       </c>
       <c r="E709" s="5" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="710" spans="1:5" x14ac:dyDescent="0.25">
@@ -17430,7 +17430,7 @@
         <v>2025</v>
       </c>
       <c r="E710" s="5" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="711" spans="1:5" x14ac:dyDescent="0.25">
@@ -17447,12 +17447,12 @@
         <v>2025</v>
       </c>
       <c r="E711" s="5" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="712" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B712" s="1" t="s">
         <v>722</v>
@@ -17464,7 +17464,7 @@
         <v>2025</v>
       </c>
       <c r="E712" s="5" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="713" spans="1:5" x14ac:dyDescent="0.25">
@@ -17481,12 +17481,12 @@
         <v>2025</v>
       </c>
       <c r="E713" s="5" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="714" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B714" s="1" t="s">
         <v>713</v>
@@ -17498,7 +17498,7 @@
         <v>2025</v>
       </c>
       <c r="E714" s="5" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="715" spans="1:5" x14ac:dyDescent="0.25">
@@ -17515,7 +17515,7 @@
         <v>2025</v>
       </c>
       <c r="E715" s="5" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="716" spans="1:5" x14ac:dyDescent="0.25">
@@ -17532,7 +17532,7 @@
         <v>2025</v>
       </c>
       <c r="E716" s="5" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="717" spans="1:5" x14ac:dyDescent="0.25">
@@ -17549,7 +17549,7 @@
         <v>2025</v>
       </c>
       <c r="E717" s="5" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="718" spans="1:5" x14ac:dyDescent="0.25">
@@ -17566,7 +17566,7 @@
         <v>2025</v>
       </c>
       <c r="E718" s="5" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="719" spans="1:5" x14ac:dyDescent="0.25">
@@ -17583,7 +17583,7 @@
         <v>2025</v>
       </c>
       <c r="E719" s="5" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="720" spans="1:5" x14ac:dyDescent="0.25">
@@ -17591,7 +17591,7 @@
         <v>326</v>
       </c>
       <c r="B720" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C720">
         <v>14</v>
@@ -17600,7 +17600,7 @@
         <v>2025</v>
       </c>
       <c r="E720" s="5" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="721" spans="1:5" x14ac:dyDescent="0.25">
@@ -17617,7 +17617,7 @@
         <v>2025</v>
       </c>
       <c r="E721" s="5" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="722" spans="1:5" x14ac:dyDescent="0.25">
@@ -17625,7 +17625,7 @@
         <v>318</v>
       </c>
       <c r="B722" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C722">
         <v>4</v>
@@ -17634,7 +17634,7 @@
         <v>2025</v>
       </c>
       <c r="E722" s="5" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="723" spans="1:5" x14ac:dyDescent="0.25">
@@ -17642,7 +17642,7 @@
         <v>342</v>
       </c>
       <c r="B723" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C723">
         <v>31</v>
@@ -17651,7 +17651,7 @@
         <v>2025</v>
       </c>
       <c r="E723" s="5" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="724" spans="1:5" x14ac:dyDescent="0.25">
@@ -17668,7 +17668,7 @@
         <v>2025</v>
       </c>
       <c r="E724" s="5" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="725" spans="1:5" x14ac:dyDescent="0.25">
@@ -17685,7 +17685,7 @@
         <v>2025</v>
       </c>
       <c r="E725" s="5" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="726" spans="1:5" x14ac:dyDescent="0.25">
@@ -17702,12 +17702,12 @@
         <v>2025</v>
       </c>
       <c r="E726" s="5" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="727" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B727" s="1" t="s">
         <v>706</v>
@@ -17719,7 +17719,7 @@
         <v>2025</v>
       </c>
       <c r="E727" s="5" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="728" spans="1:5" x14ac:dyDescent="0.25">
@@ -17736,7 +17736,7 @@
         <v>2025</v>
       </c>
       <c r="E728" s="5" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="729" spans="1:5" x14ac:dyDescent="0.25">
@@ -17753,7 +17753,7 @@
         <v>2025</v>
       </c>
       <c r="E729" s="5" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="730" spans="1:5" x14ac:dyDescent="0.25">
@@ -17770,7 +17770,7 @@
         <v>2025</v>
       </c>
       <c r="E730" s="5" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="731" spans="1:5" x14ac:dyDescent="0.25">
@@ -17787,12 +17787,12 @@
         <v>2025</v>
       </c>
       <c r="E731" s="5" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="732" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B732" s="1" t="s">
         <v>708</v>
@@ -17804,7 +17804,7 @@
         <v>2025</v>
       </c>
       <c r="E732" s="5" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="733" spans="1:5" x14ac:dyDescent="0.25">
@@ -17821,7 +17821,7 @@
         <v>2025</v>
       </c>
       <c r="E733" s="5" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="734" spans="1:5" x14ac:dyDescent="0.25">
@@ -17838,7 +17838,7 @@
         <v>2025</v>
       </c>
       <c r="E734" s="5" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="735" spans="1:5" x14ac:dyDescent="0.25">
@@ -17855,7 +17855,7 @@
         <v>2025</v>
       </c>
       <c r="E735" s="5" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="736" spans="1:5" x14ac:dyDescent="0.25">
@@ -17872,7 +17872,7 @@
         <v>2025</v>
       </c>
       <c r="E736" s="5" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="737" spans="1:5" x14ac:dyDescent="0.25">
@@ -17889,7 +17889,7 @@
         <v>2025</v>
       </c>
       <c r="E737" s="5" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="738" spans="1:5" x14ac:dyDescent="0.25">
@@ -17906,7 +17906,7 @@
         <v>2025</v>
       </c>
       <c r="E738" s="5" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="739" spans="1:5" x14ac:dyDescent="0.25">
@@ -17923,12 +17923,12 @@
         <v>2025</v>
       </c>
       <c r="E739" s="5" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="740" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B740" s="1" t="s">
         <v>710</v>
@@ -17940,7 +17940,7 @@
         <v>2025</v>
       </c>
       <c r="E740" s="5" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="741" spans="1:5" x14ac:dyDescent="0.25">
@@ -17948,7 +17948,7 @@
         <v>324</v>
       </c>
       <c r="B741" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C741">
         <v>12</v>
@@ -17957,7 +17957,7 @@
         <v>2025</v>
       </c>
       <c r="E741" s="5" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="742" spans="1:5" x14ac:dyDescent="0.25">
@@ -17974,7 +17974,7 @@
         <v>2025</v>
       </c>
       <c r="E742" s="5" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="743" spans="1:5" x14ac:dyDescent="0.25">
@@ -17991,7 +17991,7 @@
         <v>2025</v>
       </c>
       <c r="E743" s="5" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="744" spans="1:5" x14ac:dyDescent="0.25">
@@ -18008,7 +18008,7 @@
         <v>2025</v>
       </c>
       <c r="E744" s="5" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="745" spans="1:5" x14ac:dyDescent="0.25">
@@ -18025,7 +18025,7 @@
         <v>2025</v>
       </c>
       <c r="E745" s="5" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="746" spans="1:5" x14ac:dyDescent="0.25">
@@ -18042,7 +18042,7 @@
         <v>2025</v>
       </c>
       <c r="E746" s="5" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="747" spans="1:5" x14ac:dyDescent="0.25">
@@ -18059,7 +18059,7 @@
         <v>2025</v>
       </c>
       <c r="E747" s="5" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="748" spans="1:5" x14ac:dyDescent="0.25">
@@ -18076,12 +18076,12 @@
         <v>2025</v>
       </c>
       <c r="E748" s="5" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="749" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B749" s="1" t="s">
         <v>159</v>
@@ -18093,7 +18093,7 @@
         <v>2025</v>
       </c>
       <c r="E749" s="5" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="750" spans="1:5" x14ac:dyDescent="0.25">
@@ -18110,7 +18110,7 @@
         <v>2025</v>
       </c>
       <c r="E750" s="5" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="751" spans="1:5" x14ac:dyDescent="0.25">
@@ -18127,7 +18127,7 @@
         <v>2025</v>
       </c>
       <c r="E751" s="5" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="752" spans="1:5" x14ac:dyDescent="0.25">
@@ -18144,7 +18144,7 @@
         <v>2025</v>
       </c>
       <c r="E752" s="5" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="753" spans="1:5" x14ac:dyDescent="0.25">
@@ -18161,7 +18161,7 @@
         <v>2025</v>
       </c>
       <c r="E753" s="5" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="754" spans="1:5" x14ac:dyDescent="0.25">
@@ -18178,7 +18178,7 @@
         <v>2025</v>
       </c>
       <c r="E754" s="5" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="755" spans="1:5" x14ac:dyDescent="0.25">
@@ -18195,12 +18195,12 @@
         <v>2025</v>
       </c>
       <c r="E755" s="5" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="756" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B756" s="1" t="s">
         <v>712</v>
@@ -18212,7 +18212,7 @@
         <v>2025</v>
       </c>
       <c r="E756" s="5" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="757" spans="1:5" x14ac:dyDescent="0.25">
@@ -18229,7 +18229,7 @@
         <v>2025</v>
       </c>
       <c r="E757" s="5" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="758" spans="1:5" x14ac:dyDescent="0.25">
@@ -18246,7 +18246,7 @@
         <v>2025</v>
       </c>
       <c r="E758" s="5" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="759" spans="1:5" x14ac:dyDescent="0.25">
@@ -18263,7 +18263,7 @@
         <v>2025</v>
       </c>
       <c r="E759" s="5" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="760" spans="1:5" x14ac:dyDescent="0.25">
@@ -18280,7 +18280,7 @@
         <v>2025</v>
       </c>
       <c r="E760" s="5" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="761" spans="1:5" x14ac:dyDescent="0.25">
@@ -18297,7 +18297,7 @@
         <v>2025</v>
       </c>
       <c r="E761" s="5" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="762" spans="1:5" x14ac:dyDescent="0.25">
@@ -18314,7 +18314,7 @@
         <v>2025</v>
       </c>
       <c r="E762" s="5" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="763" spans="1:5" x14ac:dyDescent="0.25">
@@ -18331,7 +18331,7 @@
         <v>2025</v>
       </c>
       <c r="E763" s="5" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="764" spans="1:5" x14ac:dyDescent="0.25">
@@ -18348,7 +18348,7 @@
         <v>2025</v>
       </c>
       <c r="E764" s="5" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="765" spans="1:5" x14ac:dyDescent="0.25">
@@ -18365,7 +18365,7 @@
         <v>2025</v>
       </c>
       <c r="E765" s="5" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="766" spans="1:5" x14ac:dyDescent="0.25">
@@ -18382,15 +18382,15 @@
         <v>2025</v>
       </c>
       <c r="E766" s="5" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="767" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B767" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C767">
         <v>45</v>
@@ -18399,7 +18399,7 @@
         <v>2025</v>
       </c>
       <c r="E767" s="5" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="768" spans="1:5" x14ac:dyDescent="0.25">
@@ -18416,7 +18416,7 @@
         <v>2025</v>
       </c>
       <c r="E768" s="5" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="769" spans="1:5" x14ac:dyDescent="0.25">
@@ -18433,7 +18433,7 @@
         <v>2025</v>
       </c>
       <c r="E769" s="5" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="770" spans="1:5" x14ac:dyDescent="0.25">
@@ -18450,7 +18450,7 @@
         <v>2025</v>
       </c>
       <c r="E770" s="5" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="771" spans="1:5" x14ac:dyDescent="0.25">
@@ -18467,7 +18467,7 @@
         <v>2025</v>
       </c>
       <c r="E771" s="5" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="772" spans="1:5" x14ac:dyDescent="0.25">
@@ -18484,7 +18484,7 @@
         <v>2025</v>
       </c>
       <c r="E772" s="5" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="773" spans="1:5" x14ac:dyDescent="0.25">
@@ -18501,7 +18501,7 @@
         <v>2025</v>
       </c>
       <c r="E773" s="5" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="774" spans="1:5" x14ac:dyDescent="0.25">
@@ -18518,7 +18518,7 @@
         <v>2025</v>
       </c>
       <c r="E774" s="5" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="775" spans="1:5" x14ac:dyDescent="0.25">
@@ -18535,7 +18535,7 @@
         <v>2025</v>
       </c>
       <c r="E775" s="5" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="776" spans="1:5" x14ac:dyDescent="0.25">
@@ -18552,7 +18552,7 @@
         <v>2025</v>
       </c>
       <c r="E776" s="5" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="777" spans="1:5" x14ac:dyDescent="0.25">
@@ -18569,7 +18569,7 @@
         <v>2025</v>
       </c>
       <c r="E777" s="5" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="778" spans="1:5" x14ac:dyDescent="0.25">
@@ -18586,7 +18586,7 @@
         <v>2025</v>
       </c>
       <c r="E778" s="5" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="779" spans="1:5" x14ac:dyDescent="0.25">
@@ -18603,12 +18603,12 @@
         <v>2025</v>
       </c>
       <c r="E779" s="5" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="780" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B780" s="1" t="s">
         <v>159</v>
@@ -18620,7 +18620,7 @@
         <v>2025</v>
       </c>
       <c r="E780" s="5" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="781" spans="1:5" x14ac:dyDescent="0.25">
@@ -18637,7 +18637,7 @@
         <v>2025</v>
       </c>
       <c r="E781" s="5" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="782" spans="1:5" x14ac:dyDescent="0.25">
@@ -18654,7 +18654,7 @@
         <v>2025</v>
       </c>
       <c r="E782" s="5" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="783" spans="1:5" x14ac:dyDescent="0.25">
@@ -18671,12 +18671,12 @@
         <v>2025</v>
       </c>
       <c r="E783" s="5" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="784" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B784" s="1" t="s">
         <v>711</v>
@@ -18688,7 +18688,7 @@
         <v>2025</v>
       </c>
       <c r="E784" s="5" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="785" spans="1:5" x14ac:dyDescent="0.25">
@@ -18705,12 +18705,12 @@
         <v>2025</v>
       </c>
       <c r="E785" s="5" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="786" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B786" s="1" t="s">
         <v>710</v>
@@ -18722,7 +18722,7 @@
         <v>2025</v>
       </c>
       <c r="E786" s="5" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="787" spans="1:5" x14ac:dyDescent="0.25">
@@ -18739,12 +18739,12 @@
         <v>2025</v>
       </c>
       <c r="E787" s="5" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="788" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B788" s="1" t="s">
         <v>712</v>
@@ -18756,7 +18756,7 @@
         <v>2025</v>
       </c>
       <c r="E788" s="5" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="789" spans="1:5" x14ac:dyDescent="0.25">
@@ -18773,12 +18773,12 @@
         <v>2025</v>
       </c>
       <c r="E789" s="5" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="790" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B790" s="1" t="s">
         <v>722</v>
@@ -18790,7 +18790,7 @@
         <v>2025</v>
       </c>
       <c r="E790" s="5" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="791" spans="1:5" x14ac:dyDescent="0.25">
@@ -18807,7 +18807,7 @@
         <v>2025</v>
       </c>
       <c r="E791" s="5" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="792" spans="1:5" x14ac:dyDescent="0.25">
@@ -18815,7 +18815,7 @@
         <v>344</v>
       </c>
       <c r="B792" s="1" t="s">
-        <v>723</v>
+        <v>1635</v>
       </c>
       <c r="C792">
         <v>33</v>
@@ -18824,7 +18824,7 @@
         <v>2025</v>
       </c>
       <c r="E792" s="5" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="793" spans="1:5" x14ac:dyDescent="0.25">
@@ -18841,7 +18841,7 @@
         <v>2025</v>
       </c>
       <c r="E793" s="5" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="794" spans="1:5" x14ac:dyDescent="0.25">
@@ -18858,7 +18858,7 @@
         <v>2025</v>
       </c>
       <c r="E794" s="5" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="795" spans="1:5" x14ac:dyDescent="0.25">
@@ -18875,7 +18875,7 @@
         <v>2025</v>
       </c>
       <c r="E795" s="5" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="796" spans="1:5" x14ac:dyDescent="0.25">
@@ -18892,7 +18892,7 @@
         <v>2025</v>
       </c>
       <c r="E796" s="5" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="797" spans="1:5" x14ac:dyDescent="0.25">
@@ -18909,7 +18909,7 @@
         <v>2025</v>
       </c>
       <c r="E797" s="5" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="798" spans="1:5" x14ac:dyDescent="0.25">
@@ -18926,7 +18926,7 @@
         <v>2025</v>
       </c>
       <c r="E798" s="5" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="799" spans="1:5" x14ac:dyDescent="0.25">
@@ -18943,7 +18943,7 @@
         <v>2025</v>
       </c>
       <c r="E799" s="5" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="800" spans="1:5" x14ac:dyDescent="0.25">
@@ -18960,7 +18960,7 @@
         <v>2025</v>
       </c>
       <c r="E800" s="5" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="801" spans="1:5" x14ac:dyDescent="0.25">
@@ -18977,7 +18977,7 @@
         <v>2025</v>
       </c>
       <c r="E801" s="5" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="802" spans="1:5" x14ac:dyDescent="0.25">
@@ -18994,12 +18994,12 @@
         <v>2025</v>
       </c>
       <c r="E802" s="5" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="803" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B803" s="1" t="s">
         <v>714</v>
@@ -19011,7 +19011,7 @@
         <v>2025</v>
       </c>
       <c r="E803" s="5" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="804" spans="1:5" x14ac:dyDescent="0.25">
@@ -19028,7 +19028,7 @@
         <v>2025</v>
       </c>
       <c r="E804" s="5" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="805" spans="1:5" x14ac:dyDescent="0.25">
@@ -19045,7 +19045,7 @@
         <v>2025</v>
       </c>
       <c r="E805" s="5" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="806" spans="1:5" x14ac:dyDescent="0.25">
@@ -19062,12 +19062,12 @@
         <v>2025</v>
       </c>
       <c r="E806" s="5" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="807" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B807" s="1" t="s">
         <v>714</v>
@@ -19079,7 +19079,7 @@
         <v>2025</v>
       </c>
       <c r="E807" s="5" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="808" spans="1:5" x14ac:dyDescent="0.25">
@@ -19096,7 +19096,7 @@
         <v>2025</v>
       </c>
       <c r="E808" s="5" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="809" spans="1:5" x14ac:dyDescent="0.25">
@@ -19113,7 +19113,7 @@
         <v>2025</v>
       </c>
       <c r="E809" s="5" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
   </sheetData>
